--- a/dwm.xlsx
+++ b/dwm.xlsx
@@ -440,28 +440,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Upl Limited</v>
+        <v>Bandhan Bank Ltd</v>
       </c>
       <c r="C2" t="str">
-        <v>UPL</v>
+        <v>BANDHANBNK</v>
       </c>
       <c r="D2" s="1">
-        <v>514.85</v>
+        <v>172</v>
       </c>
       <c r="E2" s="2">
-        <v>5.4</v>
+        <v>9.21</v>
       </c>
       <c r="F2" s="2">
-        <v>5.4</v>
+        <v>9.55</v>
       </c>
       <c r="G2" s="2">
-        <v>-4.61</v>
+        <v>-3.5</v>
       </c>
       <c r="H2" s="2">
-        <v>-35.25</v>
+        <v>17.95</v>
       </c>
       <c r="I2" s="1">
-        <v>3084920</v>
+        <v>51540585</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -472,28 +472,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Ather Energy Ltd</v>
+        <v>Hcl Technologies Limited</v>
       </c>
       <c r="C3" t="str">
-        <v>ATHERENERG</v>
+        <v>HCLTECH</v>
       </c>
       <c r="D3" s="1">
-        <v>1511</v>
+        <v>1320.1</v>
       </c>
       <c r="E3" s="2">
-        <v>5.34</v>
+        <v>7.94</v>
       </c>
       <c r="F3" s="2">
-        <v>5.34</v>
+        <v>8.5</v>
       </c>
       <c r="G3" s="2">
-        <v>6.04</v>
+        <v>7.33</v>
       </c>
       <c r="H3" s="2">
-        <v>100.2</v>
+        <v>-18.68</v>
       </c>
       <c r="I3" s="1">
-        <v>3581450</v>
+        <v>21554061</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -504,28 +504,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Suzlon Energy Limited</v>
+        <v>KPIT Technologies Ltd</v>
       </c>
       <c r="C4" t="str">
-        <v>SUZLON</v>
+        <v>KPITTECH</v>
       </c>
       <c r="D4" s="1">
-        <v>39.57</v>
+        <v>513.75</v>
       </c>
       <c r="E4" s="2">
-        <v>5.24</v>
+        <v>6.81</v>
       </c>
       <c r="F4" s="2">
-        <v>5.24</v>
+        <v>7.25</v>
       </c>
       <c r="G4" s="2">
-        <v>0.2</v>
+        <v>2.94</v>
       </c>
       <c r="H4" s="2">
-        <v>-24.87</v>
+        <v>-56.18</v>
       </c>
       <c r="I4" s="1">
-        <v>141845798</v>
+        <v>6098079</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -536,28 +536,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Tata Elxsi Limited</v>
+        <v>Tata Consultancy Services Limited</v>
       </c>
       <c r="C5" t="str">
-        <v>TATAELXSI</v>
+        <v>TCS</v>
       </c>
       <c r="D5" s="1">
-        <v>3257</v>
+        <v>2262</v>
       </c>
       <c r="E5" s="2">
-        <v>4.06</v>
+        <v>6.45</v>
       </c>
       <c r="F5" s="2">
-        <v>4.06</v>
+        <v>4.92</v>
       </c>
       <c r="G5" s="2">
-        <v>5.44</v>
+        <v>10.31</v>
       </c>
       <c r="H5" s="2">
-        <v>-37.85</v>
+        <v>-29.45</v>
       </c>
       <c r="I5" s="1">
-        <v>794936</v>
+        <v>10836615</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -568,28 +568,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Indian Railway Finance Corporation Ltd</v>
+        <v>Shriram Finance Ltd</v>
       </c>
       <c r="C6" t="str">
-        <v>IRFC</v>
+        <v>SHRIRAMFIN</v>
       </c>
       <c r="D6" s="1">
-        <v>77.5</v>
+        <v>986.2</v>
       </c>
       <c r="E6" s="2">
-        <v>3.75</v>
+        <v>6.11</v>
       </c>
       <c r="F6" s="2">
-        <v>3.75</v>
+        <v>4.86</v>
       </c>
       <c r="G6" s="2">
-        <v>-2.25</v>
+        <v>0.36</v>
       </c>
       <c r="H6" s="2">
-        <v>-37.81</v>
+        <v>-1</v>
       </c>
       <c r="I6" s="1">
-        <v>17109967</v>
+        <v>7934208</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -600,28 +600,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Pnb Housing Finance Limited</v>
+        <v>Tata Elxsi Limited</v>
       </c>
       <c r="C7" t="str">
-        <v>PNBHOUSING</v>
+        <v>TATAELXSI</v>
       </c>
       <c r="D7" s="1">
-        <v>1200</v>
+        <v>3425</v>
       </c>
       <c r="E7" s="2">
-        <v>3.63</v>
+        <v>5.16</v>
       </c>
       <c r="F7" s="2">
-        <v>3.63</v>
+        <v>9.42</v>
       </c>
       <c r="G7" s="2">
-        <v>7.14</v>
+        <v>10.88</v>
       </c>
       <c r="H7" s="2">
-        <v>26.12</v>
+        <v>-34.64</v>
       </c>
       <c r="I7" s="1">
-        <v>1808660</v>
+        <v>1034545</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -632,28 +632,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Angel One Ltd</v>
+        <v>Mphasis Limited</v>
       </c>
       <c r="C8" t="str">
-        <v>ANGELONE</v>
+        <v>MPHASIS</v>
       </c>
       <c r="D8" s="1">
-        <v>302.25</v>
+        <v>2466</v>
       </c>
       <c r="E8" s="2">
-        <v>3.51</v>
+        <v>4.78</v>
       </c>
       <c r="F8" s="2">
-        <v>3.51</v>
+        <v>4.49</v>
       </c>
       <c r="G8" s="2">
-        <v>10.31</v>
+        <v>14.46</v>
       </c>
       <c r="H8" s="2">
-        <v>28.95</v>
+        <v>-11.65</v>
       </c>
       <c r="I8" s="1">
-        <v>6496974</v>
+        <v>1098438</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -664,28 +664,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>PB Fintech Ltd</v>
+        <v>Crompton Greaves Consumer Electricals Limited</v>
       </c>
       <c r="C9" t="str">
-        <v>POLICYBZR</v>
+        <v>CROMPTON</v>
       </c>
       <c r="D9" s="1">
-        <v>1047</v>
+        <v>212.02</v>
       </c>
       <c r="E9" s="2">
-        <v>3.46</v>
+        <v>4.7</v>
       </c>
       <c r="F9" s="2">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="G9" s="2">
-        <v>-1.59</v>
+        <v>1.61</v>
       </c>
       <c r="H9" s="2">
-        <v>-42.65</v>
+        <v>-15.95</v>
       </c>
       <c r="I9" s="1">
-        <v>2985015</v>
+        <v>9712295</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -696,28 +696,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>One 97 Communications Ltd</v>
+        <v>Tech Mahindra Limited</v>
       </c>
       <c r="C10" t="str">
-        <v>PAYTM</v>
+        <v>TECHM</v>
       </c>
       <c r="D10" s="1">
-        <v>1690</v>
+        <v>1540</v>
       </c>
       <c r="E10" s="2">
-        <v>3.3</v>
+        <v>4.69</v>
       </c>
       <c r="F10" s="2">
-        <v>3.3</v>
+        <v>1.71</v>
       </c>
       <c r="G10" s="2">
-        <v>0.72</v>
+        <v>1.05</v>
       </c>
       <c r="H10" s="2">
-        <v>30.11</v>
+        <v>-3.2</v>
       </c>
       <c r="I10" s="1">
-        <v>2236195</v>
+        <v>3179170</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -728,28 +728,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Power Finance Corporation Limited</v>
+        <v>Mazagon Dock Shipbuilders Ltd</v>
       </c>
       <c r="C11" t="str">
-        <v>PFC</v>
+        <v>MAZDOCK</v>
       </c>
       <c r="D11" s="1">
-        <v>337.9</v>
+        <v>2121.2</v>
       </c>
       <c r="E11" s="2">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="F11" s="2">
-        <v>3.08</v>
+        <v>5.53</v>
       </c>
       <c r="G11" s="2">
-        <v>3.81</v>
+        <v>0.39</v>
       </c>
       <c r="H11" s="2">
-        <v>-4.92</v>
+        <v>-14.82</v>
       </c>
       <c r="I11" s="1">
-        <v>6955063</v>
+        <v>840134</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -760,28 +760,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Lic Housing Finance Limited</v>
+        <v>Ujjivan Small Finance Bank Ltd</v>
       </c>
       <c r="C12" t="str">
-        <v>LICHSGFIN</v>
+        <v>UJJIVANSFB</v>
       </c>
       <c r="D12" s="1">
-        <v>568</v>
+        <v>65.25</v>
       </c>
       <c r="E12" s="2">
-        <v>2.96</v>
+        <v>4.65</v>
       </c>
       <c r="F12" s="2">
-        <v>2.96</v>
+        <v>6.18</v>
       </c>
       <c r="G12" s="2">
-        <v>7.13</v>
+        <v>-3.33</v>
       </c>
       <c r="H12" s="2">
-        <v>5.27</v>
+        <v>23.14</v>
       </c>
       <c r="I12" s="1">
-        <v>3553143</v>
+        <v>17186119</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -792,28 +792,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Delhivery Ltd</v>
+        <v>LTIMindtree Ltd</v>
       </c>
       <c r="C13" t="str">
-        <v>DELHIVERY</v>
+        <v>LTM</v>
       </c>
       <c r="D13" s="1">
-        <v>412.15</v>
+        <v>4203</v>
       </c>
       <c r="E13" s="2">
-        <v>2.91</v>
+        <v>4.58</v>
       </c>
       <c r="F13" s="2">
-        <v>2.91</v>
+        <v>3.27</v>
       </c>
       <c r="G13" s="2">
-        <v>0.6</v>
+        <v>3.91</v>
       </c>
       <c r="H13" s="2">
-        <v>2.06</v>
+        <v>-30.68</v>
       </c>
       <c r="I13" s="1">
-        <v>10532034</v>
+        <v>497405</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -824,28 +824,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>KFin Technologies Ltd</v>
+        <v>Waaree Energies Ltd</v>
       </c>
       <c r="C14" t="str">
-        <v>KFINTECH</v>
+        <v>WAAREEENER</v>
       </c>
       <c r="D14" s="1">
-        <v>866</v>
+        <v>2451</v>
       </c>
       <c r="E14" s="2">
-        <v>2.81</v>
+        <v>4.52</v>
       </c>
       <c r="F14" s="2">
-        <v>2.81</v>
+        <v>5.51</v>
       </c>
       <c r="G14" s="2">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="H14" s="2">
-        <v>-19.96</v>
+        <v>-17.42</v>
       </c>
       <c r="I14" s="1">
-        <v>596173</v>
+        <v>1104608</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -856,28 +856,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Dr. Reddy's Laboratories Limited</v>
+        <v>Coforge (Niit Tech) Ltd</v>
       </c>
       <c r="C15" t="str">
-        <v>DRREDDY</v>
+        <v>COFORGE</v>
       </c>
       <c r="D15" s="1">
-        <v>1229.4</v>
+        <v>1929</v>
       </c>
       <c r="E15" s="2">
-        <v>2.71</v>
+        <v>4.46</v>
       </c>
       <c r="F15" s="2">
-        <v>2.71</v>
+        <v>3.27</v>
       </c>
       <c r="G15" s="2">
-        <v>-0.29</v>
+        <v>10.29</v>
       </c>
       <c r="H15" s="2">
-        <v>-3.3</v>
+        <v>16</v>
       </c>
       <c r="I15" s="1">
-        <v>1756682</v>
+        <v>3771048</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -888,28 +888,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Bajaj Auto Limited</v>
+        <v>Wipro Limited</v>
       </c>
       <c r="C16" t="str">
-        <v>BAJAJ-AUTO</v>
+        <v>WIPRO</v>
       </c>
       <c r="D16" s="1">
-        <v>10034</v>
+        <v>168.6</v>
       </c>
       <c r="E16" s="2">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="F16" s="2">
-        <v>2.62</v>
+        <v>3.71</v>
       </c>
       <c r="G16" s="2">
-        <v>-7.72</v>
+        <v>6.37</v>
       </c>
       <c r="H16" s="2">
-        <v>7.4</v>
+        <v>-35.96</v>
       </c>
       <c r="I16" s="1">
-        <v>313934</v>
+        <v>18801973</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -920,28 +920,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Samvardhana Motherson International Ltd</v>
+        <v>Inox Wind Limited</v>
       </c>
       <c r="C17" t="str">
-        <v>MOTHERSON</v>
+        <v>INOXWIND</v>
       </c>
       <c r="D17" s="1">
-        <v>156.99</v>
+        <v>69.98</v>
       </c>
       <c r="E17" s="2">
-        <v>2.61</v>
+        <v>4.18</v>
       </c>
       <c r="F17" s="2">
-        <v>2.61</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2">
-        <v>-3.84</v>
+        <v>0.68</v>
       </c>
       <c r="H17" s="2">
-        <v>30.89</v>
+        <v>-43.35</v>
       </c>
       <c r="I17" s="1">
-        <v>7845512</v>
+        <v>10754500</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -952,28 +952,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Pg Electroplast Limited</v>
+        <v>Infosys Limited</v>
       </c>
       <c r="C18" t="str">
-        <v>PGEL</v>
+        <v>INFY</v>
       </c>
       <c r="D18" s="1">
-        <v>525</v>
+        <v>1061.15</v>
       </c>
       <c r="E18" s="2">
-        <v>2.58</v>
+        <v>4.03</v>
       </c>
       <c r="F18" s="2">
-        <v>2.58</v>
+        <v>3.69</v>
       </c>
       <c r="G18" s="2">
-        <v>6.39</v>
+        <v>6.74</v>
       </c>
       <c r="H18" s="2">
-        <v>-8.74</v>
+        <v>-34.31</v>
       </c>
       <c r="I18" s="1">
-        <v>1695763</v>
+        <v>21277720</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -984,28 +984,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Motilal Oswal Financial Services Limited</v>
+        <v>Persistent Systems Limited</v>
       </c>
       <c r="C19" t="str">
-        <v>MOTILALOFS</v>
+        <v>PERSISTENT</v>
       </c>
       <c r="D19" s="1">
-        <v>1051</v>
+        <v>5984</v>
       </c>
       <c r="E19" s="2">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="F19" s="2">
-        <v>2.44</v>
+        <v>3.71</v>
       </c>
       <c r="G19" s="2">
-        <v>5.73</v>
+        <v>13.35</v>
       </c>
       <c r="H19" s="2">
-        <v>22.82</v>
+        <v>-4.59</v>
       </c>
       <c r="I19" s="1">
-        <v>953453</v>
+        <v>1004147</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1016,28 +1016,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Bosch Limited</v>
+        <v>Bharat Dynamics Ltd</v>
       </c>
       <c r="C20" t="str">
-        <v>BOSCHLTD</v>
+        <v>BDL</v>
       </c>
       <c r="D20" s="1">
-        <v>44585</v>
+        <v>1125.9</v>
       </c>
       <c r="E20" s="2">
-        <v>2.39</v>
+        <v>3.39</v>
       </c>
       <c r="F20" s="2">
-        <v>2.39</v>
+        <v>4.65</v>
       </c>
       <c r="G20" s="2">
-        <v>-5.34</v>
+        <v>1.42</v>
       </c>
       <c r="H20" s="2">
-        <v>23.71</v>
+        <v>-23.23</v>
       </c>
       <c r="I20" s="1">
-        <v>20332</v>
+        <v>796711</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1048,28 +1048,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Anand Rathi Wealth Ltd</v>
+        <v>Prestige Estates Projects Limited</v>
       </c>
       <c r="C21" t="str">
-        <v>ANANDRATHI</v>
+        <v>PRESTIGE</v>
       </c>
       <c r="D21" s="1">
-        <v>2087</v>
+        <v>1477.7</v>
       </c>
       <c r="E21" s="2">
-        <v>2.37</v>
+        <v>3.37</v>
       </c>
       <c r="F21" s="2">
-        <v>2.37</v>
+        <v>5.04</v>
       </c>
       <c r="G21" s="2">
-        <v>-1.56</v>
+        <v>-0.28</v>
       </c>
       <c r="H21" s="2">
-        <v>34.11</v>
+        <v>-7.34</v>
       </c>
       <c r="I21" s="1">
-        <v>932366</v>
+        <v>394293</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1080,28 +1080,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Kalyan Jewellers India Ltd</v>
+        <v>Indian Renewable Energy Development Agency Ltd</v>
       </c>
       <c r="C22" t="str">
-        <v>KALYANKJIL</v>
+        <v>IREDA</v>
       </c>
       <c r="D22" s="1">
-        <v>567.15</v>
+        <v>108</v>
       </c>
       <c r="E22" s="2">
-        <v>2.37</v>
+        <v>3.25</v>
       </c>
       <c r="F22" s="2">
-        <v>2.37</v>
+        <v>3.45</v>
       </c>
       <c r="G22" s="2">
-        <v>2.53</v>
+        <v>-3.3</v>
       </c>
       <c r="H22" s="2">
-        <v>16.85</v>
+        <v>-22.8</v>
       </c>
       <c r="I22" s="1">
-        <v>5100358</v>
+        <v>5520345</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1112,28 +1112,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Hitachi Energy India Ltd</v>
+        <v>Hindustan Unilever Limited</v>
       </c>
       <c r="C23" t="str">
-        <v>POWERINDIA</v>
+        <v>HINDUNILVR</v>
       </c>
       <c r="D23" s="1">
-        <v>31290</v>
+        <v>1876.6</v>
       </c>
       <c r="E23" s="2">
-        <v>2.24</v>
+        <v>3.07</v>
       </c>
       <c r="F23" s="2">
-        <v>2.24</v>
+        <v>1.07</v>
       </c>
       <c r="G23" s="2">
-        <v>2.15</v>
+        <v>-0.13</v>
       </c>
       <c r="H23" s="2">
-        <v>70.89</v>
+        <v>-18.97</v>
       </c>
       <c r="I23" s="1">
-        <v>64189</v>
+        <v>2074804</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1144,28 +1144,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Hindustan Aeronautics Ltd</v>
+        <v>Bajaj Auto Limited</v>
       </c>
       <c r="C24" t="str">
-        <v>HAL</v>
+        <v>BAJAJ-AUTO</v>
       </c>
       <c r="D24" s="1">
-        <v>4760</v>
+        <v>10336</v>
       </c>
       <c r="E24" s="2">
-        <v>2.24</v>
+        <v>3.01</v>
       </c>
       <c r="F24" s="2">
-        <v>2.24</v>
+        <v>5.71</v>
       </c>
       <c r="G24" s="2">
-        <v>1.97</v>
+        <v>-4.95</v>
       </c>
       <c r="H24" s="2">
-        <v>8.46</v>
+        <v>10.63</v>
       </c>
       <c r="I24" s="1">
-        <v>527818</v>
+        <v>332124</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1176,28 +1176,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Multi Commodity Exchange Of India Limited</v>
+        <v>Computer Age Management Services Ltd</v>
       </c>
       <c r="C25" t="str">
-        <v>MCX</v>
+        <v>CAMS</v>
       </c>
       <c r="D25" s="1">
-        <v>3390</v>
+        <v>699.5</v>
       </c>
       <c r="E25" s="2">
-        <v>2.16</v>
+        <v>3.01</v>
       </c>
       <c r="F25" s="2">
-        <v>2.16</v>
+        <v>4.01</v>
       </c>
       <c r="G25" s="2">
-        <v>2.71</v>
+        <v>4.25</v>
       </c>
       <c r="H25" s="2">
-        <v>52.21</v>
+        <v>-5.59</v>
       </c>
       <c r="I25" s="1">
-        <v>1699974</v>
+        <v>1582418</v>
       </c>
       <c r="J25" t="str">
         <v/>
@@ -1208,28 +1208,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Apl Apollo Tubes Limited</v>
+        <v>National Aluminium Company Limited</v>
       </c>
       <c r="C26" t="str">
-        <v>APLAPOLLO</v>
+        <v>NATIONALUM</v>
       </c>
       <c r="D26" s="1">
-        <v>2157.4</v>
+        <v>319.5</v>
       </c>
       <c r="E26" s="2">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="F26" s="2">
-        <v>2.05</v>
+        <v>1.14</v>
       </c>
       <c r="G26" s="2">
-        <v>-1.49</v>
+        <v>-6.29</v>
       </c>
       <c r="H26" s="2">
-        <v>12.72</v>
+        <v>1.65</v>
       </c>
       <c r="I26" s="1">
-        <v>286344</v>
+        <v>4772190</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -1240,28 +1240,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>360 ONE WAM Ltd</v>
+        <v>Cochin Shipyard Ltd</v>
       </c>
       <c r="C27" t="str">
-        <v>360ONE</v>
+        <v>COCHINSHIP</v>
       </c>
       <c r="D27" s="1">
-        <v>1068.7</v>
+        <v>1266</v>
       </c>
       <c r="E27" s="2">
-        <v>1.98</v>
+        <v>2.76</v>
       </c>
       <c r="F27" s="2">
-        <v>1.98</v>
+        <v>2.93</v>
       </c>
       <c r="G27" s="2">
-        <v>3.76</v>
+        <v>-3.73</v>
       </c>
       <c r="H27" s="2">
-        <v>-10.19</v>
+        <v>-21.86</v>
       </c>
       <c r="I27" s="1">
-        <v>330899</v>
+        <v>725923</v>
       </c>
       <c r="J27" t="str">
         <v/>
@@ -1272,28 +1272,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Nbcc (india) Limited</v>
+        <v>Indian Railway Finance Corporation Ltd</v>
       </c>
       <c r="C28" t="str">
-        <v>NBCC</v>
+        <v>IRFC</v>
       </c>
       <c r="D28" s="1">
-        <v>75.92</v>
+        <v>79.64</v>
       </c>
       <c r="E28" s="2">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="F28" s="2">
-        <v>1.96</v>
+        <v>6.61</v>
       </c>
       <c r="G28" s="2">
-        <v>-3.29</v>
+        <v>0.45</v>
       </c>
       <c r="H28" s="2">
-        <v>-37.65</v>
+        <v>-36.09</v>
       </c>
       <c r="I28" s="1">
-        <v>4956073</v>
+        <v>14375720</v>
       </c>
       <c r="J28" t="str">
         <v/>
@@ -1304,28 +1304,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Hindustan Petroleum Corporation Limited</v>
+        <v>Godrej Properties Limited</v>
       </c>
       <c r="C29" t="str">
-        <v>HINDPETRO</v>
+        <v>GODREJPROP</v>
       </c>
       <c r="D29" s="1">
-        <v>332.25</v>
+        <v>1586.3</v>
       </c>
       <c r="E29" s="2">
-        <v>1.92</v>
+        <v>2.71</v>
       </c>
       <c r="F29" s="2">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="G29" s="2">
-        <v>-5.17</v>
+        <v>-2.59</v>
       </c>
       <c r="H29" s="2">
-        <v>-33.42</v>
+        <v>-20.86</v>
       </c>
       <c r="I29" s="1">
-        <v>5155642</v>
+        <v>364851</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -1336,28 +1336,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Tvs Motor Company Limited</v>
+        <v>Indusind Bank Limited</v>
       </c>
       <c r="C30" t="str">
-        <v>TVSMOTOR</v>
+        <v>INDUSINDBK</v>
       </c>
       <c r="D30" s="1">
-        <v>3940.3</v>
+        <v>875.55</v>
       </c>
       <c r="E30" s="2">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="F30" s="2">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="G30" s="2">
-        <v>-4.04</v>
+        <v>-2.87</v>
       </c>
       <c r="H30" s="2">
-        <v>5.93</v>
+        <v>1.31</v>
       </c>
       <c r="I30" s="1">
-        <v>690998</v>
+        <v>5236035</v>
       </c>
       <c r="J30" t="str">
         <v/>
@@ -1368,28 +1368,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Sona BLW Precision Forgings Ltd</v>
+        <v>Indian Bank Ltd</v>
       </c>
       <c r="C31" t="str">
-        <v>SONACOMS</v>
+        <v>INDIANB</v>
       </c>
       <c r="D31" s="1">
-        <v>798</v>
+        <v>835.6</v>
       </c>
       <c r="E31" s="2">
-        <v>1.88</v>
+        <v>2.64</v>
       </c>
       <c r="F31" s="2">
-        <v>1.88</v>
+        <v>0.7</v>
       </c>
       <c r="G31" s="2">
-        <v>-3.86</v>
+        <v>3.69</v>
       </c>
       <c r="H31" s="2">
-        <v>66.46</v>
+        <v>-0.2</v>
       </c>
       <c r="I31" s="1">
-        <v>2043561</v>
+        <v>2361186</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1400,28 +1400,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>Polycab India Ltd</v>
+        <v>Angel One Ltd</v>
       </c>
       <c r="C32" t="str">
-        <v>POLYCAB</v>
+        <v>ANGELONE</v>
       </c>
       <c r="D32" s="1">
-        <v>8405</v>
+        <v>310.1</v>
       </c>
       <c r="E32" s="2">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="F32" s="2">
-        <v>1.82</v>
+        <v>6.2</v>
       </c>
       <c r="G32" s="2">
-        <v>4.72</v>
+        <v>13.18</v>
       </c>
       <c r="H32" s="2">
-        <v>10.32</v>
+        <v>32.3</v>
       </c>
       <c r="I32" s="1">
-        <v>456246</v>
+        <v>6602388</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1432,28 +1432,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>Solar Industries India Limited</v>
+        <v>The Phoenix Mills Limited</v>
       </c>
       <c r="C33" t="str">
-        <v>SOLARINDS</v>
+        <v>PHOENIXLTD</v>
       </c>
       <c r="D33" s="1">
-        <v>20334</v>
+        <v>1887</v>
       </c>
       <c r="E33" s="2">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="F33" s="2">
-        <v>1.67</v>
+        <v>4.08</v>
       </c>
       <c r="G33" s="2">
-        <v>3.22</v>
+        <v>-2.48</v>
       </c>
       <c r="H33" s="2">
-        <v>65.96</v>
+        <v>1.81</v>
       </c>
       <c r="I33" s="1">
-        <v>127193</v>
+        <v>595407</v>
       </c>
       <c r="J33" t="str">
         <v/>
@@ -1464,28 +1464,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>Manappuram Finance Limited</v>
+        <v>KFin Technologies Ltd</v>
       </c>
       <c r="C34" t="str">
-        <v>MANAPPURAM</v>
+        <v>KFINTECH</v>
       </c>
       <c r="D34" s="1">
-        <v>320</v>
+        <v>888</v>
       </c>
       <c r="E34" s="2">
-        <v>1.65</v>
+        <v>2.54</v>
       </c>
       <c r="F34" s="2">
-        <v>1.65</v>
+        <v>5.42</v>
       </c>
       <c r="G34" s="2">
-        <v>1.31</v>
+        <v>5.71</v>
       </c>
       <c r="H34" s="2">
-        <v>3.71</v>
+        <v>-17.93</v>
       </c>
       <c r="I34" s="1">
-        <v>5000299</v>
+        <v>1611120</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -1496,28 +1496,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>Siemens Limited</v>
+        <v>Bajaj Finance Limited</v>
       </c>
       <c r="C35" t="str">
-        <v>SIEMENS</v>
+        <v>BAJFINANCE</v>
       </c>
       <c r="D35" s="1">
-        <v>3654</v>
+        <v>981.5</v>
       </c>
       <c r="E35" s="2">
-        <v>1.64</v>
+        <v>2.53</v>
       </c>
       <c r="F35" s="2">
-        <v>1.64</v>
+        <v>2.24</v>
       </c>
       <c r="G35" s="2">
-        <v>-1.92</v>
+        <v>2.3</v>
       </c>
       <c r="H35" s="2">
-        <v>19.28</v>
+        <v>-0.54</v>
       </c>
       <c r="I35" s="1">
-        <v>212247</v>
+        <v>7322684</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -1528,28 +1528,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>Tata Motors Passenger Vehicles Ltd</v>
+        <v>Trent Limited</v>
       </c>
       <c r="C36" t="str">
-        <v>TMPV</v>
+        <v>TRENT</v>
       </c>
       <c r="D36" s="1">
-        <v>284.45</v>
+        <v>2985.9</v>
       </c>
       <c r="E36" s="2">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="F36" s="2">
-        <v>1.63</v>
+        <v>2.32</v>
       </c>
       <c r="G36" s="2">
-        <v>0.34</v>
+        <v>13.9</v>
       </c>
       <c r="H36" s="2">
-        <v>-22.57</v>
+        <v>4.67</v>
       </c>
       <c r="I36" s="1">
-        <v>9423664</v>
+        <v>863706</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -1560,28 +1560,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>Prestige Estates Projects Limited</v>
+        <v>Havells India Limited</v>
       </c>
       <c r="C37" t="str">
-        <v>PRESTIGE</v>
+        <v>HAVELLS</v>
       </c>
       <c r="D37" s="1">
-        <v>1429.5</v>
+        <v>1078.3</v>
       </c>
       <c r="E37" s="2">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="F37" s="2">
-        <v>1.61</v>
+        <v>3.53</v>
       </c>
       <c r="G37" s="2">
-        <v>-3.54</v>
+        <v>6.13</v>
       </c>
       <c r="H37" s="2">
-        <v>-10.36</v>
+        <v>-24.32</v>
       </c>
       <c r="I37" s="1">
-        <v>494685</v>
+        <v>597404</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -1592,28 +1592,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>Laurus Labs Limited</v>
+        <v>Cholamandalam Investment And Finance Company Limited</v>
       </c>
       <c r="C38" t="str">
-        <v>LAURUSLABS</v>
+        <v>CHOLAFIN</v>
       </c>
       <c r="D38" s="1">
-        <v>2069.2</v>
+        <v>1620</v>
       </c>
       <c r="E38" s="2">
-        <v>1.6</v>
+        <v>2.49</v>
       </c>
       <c r="F38" s="2">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="G38" s="2">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2">
-        <v>86.75</v>
+        <v>-4.83</v>
       </c>
       <c r="I38" s="1">
-        <v>1417097</v>
+        <v>1735701</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -1624,28 +1624,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>Bharat Electronics Limited</v>
+        <v>Hindustan Aeronautics Ltd</v>
       </c>
       <c r="C39" t="str">
-        <v>BEL</v>
+        <v>HAL</v>
       </c>
       <c r="D39" s="1">
-        <v>373.9</v>
+        <v>4874.5</v>
       </c>
       <c r="E39" s="2">
-        <v>1.56</v>
+        <v>2.41</v>
       </c>
       <c r="F39" s="2">
-        <v>1.56</v>
+        <v>4.7</v>
       </c>
       <c r="G39" s="2">
-        <v>-3.71</v>
+        <v>4.42</v>
       </c>
       <c r="H39" s="2">
-        <v>-6.43</v>
+        <v>11.07</v>
       </c>
       <c r="I39" s="1">
-        <v>8428541</v>
+        <v>593734</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -1656,28 +1656,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>Kei Industries Limited</v>
+        <v>SBI Cards &amp; Payment Services Ltd</v>
       </c>
       <c r="C40" t="str">
-        <v>KEI</v>
+        <v>SBICARD</v>
       </c>
       <c r="D40" s="1">
-        <v>4654.2</v>
+        <v>572.1</v>
       </c>
       <c r="E40" s="2">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="F40" s="2">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="G40" s="2">
-        <v>4.47</v>
+        <v>-1.03</v>
       </c>
       <c r="H40" s="2">
-        <v>4.35</v>
+        <v>-33.61</v>
       </c>
       <c r="I40" s="1">
-        <v>230372</v>
+        <v>493560</v>
       </c>
       <c r="J40" t="str">
         <v/>
@@ -1688,28 +1688,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>Zydus Lifesciences Ltd</v>
+        <v>Rail Vikas Nigam Ltd</v>
       </c>
       <c r="C41" t="str">
-        <v>ZYDUSLIFE</v>
+        <v>RVNL</v>
       </c>
       <c r="D41" s="1">
-        <v>1134.4</v>
+        <v>197.3</v>
       </c>
       <c r="E41" s="2">
-        <v>1.51</v>
+        <v>2.37</v>
       </c>
       <c r="F41" s="2">
-        <v>1.51</v>
+        <v>3.49</v>
       </c>
       <c r="G41" s="2">
-        <v>-2.38</v>
+        <v>-2.21</v>
       </c>
       <c r="H41" s="2">
-        <v>24.07</v>
+        <v>-44.77</v>
       </c>
       <c r="I41" s="1">
-        <v>789716</v>
+        <v>3433927</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -1720,28 +1720,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>Premier Energies Ltd</v>
+        <v>Oracle Financial Services Software Limited</v>
       </c>
       <c r="C42" t="str">
-        <v>PREMIERENE</v>
+        <v>OFSS</v>
       </c>
       <c r="D42" s="1">
-        <v>908.85</v>
+        <v>10603</v>
       </c>
       <c r="E42" s="2">
-        <v>1.51</v>
+        <v>2.35</v>
       </c>
       <c r="F42" s="2">
-        <v>1.51</v>
+        <v>0.88</v>
       </c>
       <c r="G42" s="2">
-        <v>4.45</v>
+        <v>-0.25</v>
       </c>
       <c r="H42" s="2">
-        <v>7.92</v>
+        <v>37.93</v>
       </c>
       <c r="I42" s="1">
-        <v>1272550</v>
+        <v>346375</v>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -1752,28 +1752,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>The Phoenix Mills Limited</v>
+        <v>Siemens Limited</v>
       </c>
       <c r="C43" t="str">
-        <v>PHOENIXLTD</v>
+        <v>SIEMENS</v>
       </c>
       <c r="D43" s="1">
-        <v>1840</v>
+        <v>3736.9</v>
       </c>
       <c r="E43" s="2">
-        <v>1.48</v>
+        <v>2.27</v>
       </c>
       <c r="F43" s="2">
-        <v>1.48</v>
+        <v>3.95</v>
       </c>
       <c r="G43" s="2">
-        <v>-4.91</v>
+        <v>0.3</v>
       </c>
       <c r="H43" s="2">
-        <v>-0.73</v>
+        <v>21.99</v>
       </c>
       <c r="I43" s="1">
-        <v>517066</v>
+        <v>107693</v>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -1784,28 +1784,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>Astral Ltd</v>
+        <v>Container Corporation Of India Limited</v>
       </c>
       <c r="C44" t="str">
-        <v>ASTRAL</v>
+        <v>CONCOR</v>
       </c>
       <c r="D44" s="1">
-        <v>1430.4</v>
+        <v>450.6</v>
       </c>
       <c r="E44" s="2">
-        <v>1.46</v>
+        <v>2.23</v>
       </c>
       <c r="F44" s="2">
-        <v>1.46</v>
+        <v>1.95</v>
       </c>
       <c r="G44" s="2">
-        <v>4.38</v>
+        <v>0.69</v>
       </c>
       <c r="H44" s="2">
-        <v>3.02</v>
+        <v>-14.16</v>
       </c>
       <c r="I44" s="1">
-        <v>459978</v>
+        <v>429174</v>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -1816,28 +1816,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>Ujjivan Small Finance Bank Ltd</v>
+        <v>Godfrey Phillips India Limited</v>
       </c>
       <c r="C45" t="str">
-        <v>UJJIVANSFB</v>
+        <v>GODFRYPHLP</v>
       </c>
       <c r="D45" s="1">
-        <v>62.35</v>
+        <v>1829.8</v>
       </c>
       <c r="E45" s="2">
-        <v>1.46</v>
+        <v>2.12</v>
       </c>
       <c r="F45" s="2">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="G45" s="2">
-        <v>-7.63</v>
+        <v>-3.28</v>
       </c>
       <c r="H45" s="2">
-        <v>17.66</v>
+        <v>-33.76</v>
       </c>
       <c r="I45" s="1">
-        <v>15602671</v>
+        <v>162517</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -1848,28 +1848,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>Adani Green Energy Ltd</v>
+        <v>Adani Enterprises Limited</v>
       </c>
       <c r="C46" t="str">
-        <v>ADANIGREEN</v>
+        <v>ADANIENT</v>
       </c>
       <c r="D46" s="1">
-        <v>1274</v>
+        <v>2685.6</v>
       </c>
       <c r="E46" s="2">
-        <v>1.45</v>
+        <v>2.11</v>
       </c>
       <c r="F46" s="2">
-        <v>1.45</v>
+        <v>1.94</v>
       </c>
       <c r="G46" s="2">
-        <v>-0.31</v>
+        <v>-7.5</v>
       </c>
       <c r="H46" s="2">
-        <v>25.5</v>
+        <v>19.91</v>
       </c>
       <c r="I46" s="1">
-        <v>1529818</v>
+        <v>1187187</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -1880,28 +1880,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>Bharat Heavy Electricals Limited</v>
+        <v>Central Depository Services Ltd</v>
       </c>
       <c r="C47" t="str">
-        <v>BHEL</v>
+        <v>CDSL</v>
       </c>
       <c r="D47" s="1">
-        <v>439.9</v>
+        <v>1292.5</v>
       </c>
       <c r="E47" s="2">
-        <v>1.45</v>
+        <v>2.09</v>
       </c>
       <c r="F47" s="2">
-        <v>1.45</v>
+        <v>2.58</v>
       </c>
       <c r="G47" s="2">
-        <v>5.87</v>
+        <v>2.25</v>
       </c>
       <c r="H47" s="2">
-        <v>53.04</v>
+        <v>-10.47</v>
       </c>
       <c r="I47" s="1">
-        <v>8403722</v>
+        <v>757542</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -1912,28 +1912,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Adani Energy Solutions Ltd</v>
+        <v>Kaynes Technology India Ltd</v>
       </c>
       <c r="C48" t="str">
-        <v>ADANIENSOL</v>
+        <v>KAYNES</v>
       </c>
       <c r="D48" s="1">
-        <v>1280</v>
+        <v>3289</v>
       </c>
       <c r="E48" s="2">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="F48" s="2">
-        <v>1.43</v>
+        <v>0.77</v>
       </c>
       <c r="G48" s="2">
-        <v>-2.63</v>
+        <v>-6.06</v>
       </c>
       <c r="H48" s="2">
-        <v>24.59</v>
+        <v>-18.04</v>
       </c>
       <c r="I48" s="1">
-        <v>789685</v>
+        <v>504854</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -1944,28 +1944,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>GE Vernova T&amp;D India Ltd</v>
+        <v>Grasim Industries Limited</v>
       </c>
       <c r="C49" t="str">
-        <v>GVT&amp;D</v>
+        <v>GRASIM</v>
       </c>
       <c r="D49" s="1">
-        <v>4254</v>
+        <v>2916.3</v>
       </c>
       <c r="E49" s="2">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="F49" s="2">
-        <v>1.42</v>
+        <v>0.91</v>
       </c>
       <c r="G49" s="2">
-        <v>1.26</v>
+        <v>-4.76</v>
       </c>
       <c r="H49" s="2">
-        <v>35.8</v>
+        <v>3.09</v>
       </c>
       <c r="I49" s="1">
-        <v>213022</v>
+        <v>311144</v>
       </c>
       <c r="J49" t="str">
         <v/>
@@ -1976,28 +1976,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>CG Power and Industrial Solutions Ltd</v>
+        <v>Jubilant Foodworks Limited</v>
       </c>
       <c r="C50" t="str">
-        <v>CGPOWER</v>
+        <v>JUBLFOOD</v>
       </c>
       <c r="D50" s="1">
-        <v>867.5</v>
+        <v>424.55</v>
       </c>
       <c r="E50" s="2">
-        <v>1.4</v>
+        <v>2.04</v>
       </c>
       <c r="F50" s="2">
-        <v>1.4</v>
+        <v>0.43</v>
       </c>
       <c r="G50" s="2">
-        <v>1.56</v>
+        <v>-7.04</v>
       </c>
       <c r="H50" s="2">
-        <v>33.89</v>
+        <v>-24</v>
       </c>
       <c r="I50" s="1">
-        <v>1507658</v>
+        <v>1086799</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -2008,28 +2008,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Mankind Pharma Ltd</v>
+        <v>Bajaj Finserv Limited</v>
       </c>
       <c r="C51" t="str">
-        <v>MANKIND</v>
+        <v>BAJAJFINSV</v>
       </c>
       <c r="D51" s="1">
-        <v>2400</v>
+        <v>1754.6</v>
       </c>
       <c r="E51" s="2">
-        <v>1.33</v>
+        <v>2.02</v>
       </c>
       <c r="F51" s="2">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="G51" s="2">
-        <v>-4.15</v>
+        <v>1.36</v>
       </c>
       <c r="H51" s="2">
-        <v>9.26</v>
+        <v>-13.99</v>
       </c>
       <c r="I51" s="1">
-        <v>205896</v>
+        <v>1559098</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2040,28 +2040,28 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>BSE (Bombay stock exchange) Ltd</v>
+        <v>Dlf Limited</v>
       </c>
       <c r="C52" t="str">
-        <v>BSE</v>
+        <v>DLF</v>
       </c>
       <c r="D52" s="1">
-        <v>3330.2</v>
+        <v>663.1</v>
       </c>
       <c r="E52" s="2">
-        <v>1.31</v>
+        <v>2.02</v>
       </c>
       <c r="F52" s="2">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="G52" s="2">
-        <v>7.7</v>
+        <v>-1.62</v>
       </c>
       <c r="H52" s="2">
-        <v>26.52</v>
+        <v>-3.54</v>
       </c>
       <c r="I52" s="1">
-        <v>3342319</v>
+        <v>2025839</v>
       </c>
       <c r="J52" t="str">
         <v/>
@@ -2072,28 +2072,28 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>Amber Enterprises India Ltd</v>
+        <v>Pnb Housing Finance Limited</v>
       </c>
       <c r="C53" t="str">
-        <v>AMBER</v>
+        <v>PNBHOUSING</v>
       </c>
       <c r="D53" s="1">
-        <v>6528</v>
+        <v>1224</v>
       </c>
       <c r="E53" s="2">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="F53" s="2">
-        <v>1.29</v>
+        <v>5.7</v>
       </c>
       <c r="G53" s="2">
-        <v>-2.17</v>
+        <v>9.29</v>
       </c>
       <c r="H53" s="2">
-        <v>2.21</v>
+        <v>28.64</v>
       </c>
       <c r="I53" s="1">
-        <v>139786</v>
+        <v>1029540</v>
       </c>
       <c r="J53" t="str">
         <v/>
@@ -2104,28 +2104,28 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>Bharat Dynamics Ltd</v>
+        <v>Ashok Leyland Limited</v>
       </c>
       <c r="C54" t="str">
-        <v>BDL</v>
+        <v>ASHOKLEY</v>
       </c>
       <c r="D54" s="1">
-        <v>1089</v>
+        <v>147.11</v>
       </c>
       <c r="E54" s="2">
-        <v>1.22</v>
+        <v>1.98</v>
       </c>
       <c r="F54" s="2">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="G54" s="2">
-        <v>-1.9</v>
+        <v>-4.59</v>
       </c>
       <c r="H54" s="2">
-        <v>-25.74</v>
+        <v>-17.9</v>
       </c>
       <c r="I54" s="1">
-        <v>509519</v>
+        <v>10463278</v>
       </c>
       <c r="J54" t="str">
         <v/>
@@ -2136,28 +2136,28 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>HDFC Asset Management Company Ltd</v>
+        <v>REC Ltd</v>
       </c>
       <c r="C55" t="str">
-        <v>HDFCAMC</v>
+        <v>RECLTD</v>
       </c>
       <c r="D55" s="1">
-        <v>2289.7</v>
+        <v>306.85</v>
       </c>
       <c r="E55" s="2">
-        <v>1.2</v>
+        <v>1.94</v>
       </c>
       <c r="F55" s="2">
-        <v>1.2</v>
+        <v>2.28</v>
       </c>
       <c r="G55" s="2">
-        <v>0.39</v>
+        <v>2.63</v>
       </c>
       <c r="H55" s="2">
-        <v>-14.31</v>
+        <v>-14</v>
       </c>
       <c r="I55" s="1">
-        <v>755157</v>
+        <v>15283839</v>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -2168,28 +2168,28 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>Nippon Life India Asset Management Ltd</v>
+        <v>Sagility India Ltd</v>
       </c>
       <c r="C56" t="str">
-        <v>NAM-INDIA</v>
+        <v>SAGILITY</v>
       </c>
       <c r="D56" s="1">
-        <v>1057</v>
+        <v>44.02</v>
       </c>
       <c r="E56" s="2">
-        <v>1.15</v>
+        <v>1.92</v>
       </c>
       <c r="F56" s="2">
-        <v>1.15</v>
+        <v>0.05</v>
       </c>
       <c r="G56" s="2">
-        <v>-1.22</v>
+        <v>3.38</v>
       </c>
       <c r="H56" s="2">
-        <v>20.16</v>
+        <v>-15.38</v>
       </c>
       <c r="I56" s="1">
-        <v>419849</v>
+        <v>12679672</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -2200,28 +2200,28 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>Abb India Limited</v>
+        <v>Lodha Developers Ltd</v>
       </c>
       <c r="C57" t="str">
-        <v>ABB</v>
+        <v>LODHA</v>
       </c>
       <c r="D57" s="1">
-        <v>6855.5</v>
+        <v>1090</v>
       </c>
       <c r="E57" s="2">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="F57" s="2">
-        <v>1.11</v>
+        <v>2.37</v>
       </c>
       <c r="G57" s="2">
-        <v>1.17</v>
+        <v>-3.96</v>
       </c>
       <c r="H57" s="2">
-        <v>32.6</v>
+        <v>2.7</v>
       </c>
       <c r="I57" s="1">
-        <v>203395</v>
+        <v>886850</v>
       </c>
       <c r="J57" t="str">
         <v/>
@@ -2232,28 +2232,28 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>Rail Vikas Nigam Ltd</v>
+        <v>Samvardhana Motherson International Ltd</v>
       </c>
       <c r="C58" t="str">
-        <v>RVNL</v>
+        <v>MOTHERSON</v>
       </c>
       <c r="D58" s="1">
-        <v>192.74</v>
+        <v>159.95</v>
       </c>
       <c r="E58" s="2">
-        <v>1.1</v>
+        <v>1.89</v>
       </c>
       <c r="F58" s="2">
-        <v>1.1</v>
+        <v>4.54</v>
       </c>
       <c r="G58" s="2">
-        <v>-4.47</v>
+        <v>-2.03</v>
       </c>
       <c r="H58" s="2">
-        <v>-46.05</v>
+        <v>33.36</v>
       </c>
       <c r="I58" s="1">
-        <v>3633357</v>
+        <v>6262472</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -2264,28 +2264,28 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>Jsw Energy Limited</v>
+        <v>Varun Beverages Limited</v>
       </c>
       <c r="C59" t="str">
-        <v>JSWENERGY</v>
+        <v>VBL</v>
       </c>
       <c r="D59" s="1">
-        <v>467.35</v>
+        <v>441.3</v>
       </c>
       <c r="E59" s="2">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="F59" s="2">
-        <v>1.09</v>
+        <v>0.07</v>
       </c>
       <c r="G59" s="2">
-        <v>-5.53</v>
+        <v>2.15</v>
       </c>
       <c r="H59" s="2">
-        <v>-3.13</v>
+        <v>-9.91</v>
       </c>
       <c r="I59" s="1">
-        <v>1556832</v>
+        <v>2449971</v>
       </c>
       <c r="J59" t="str">
         <v/>
@@ -2296,28 +2296,28 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>Havells India Limited</v>
+        <v>Tvs Motor Company Limited</v>
       </c>
       <c r="C60" t="str">
-        <v>HAVELLS</v>
+        <v>TVSMOTOR</v>
       </c>
       <c r="D60" s="1">
-        <v>1052</v>
+        <v>4012.7</v>
       </c>
       <c r="E60" s="2">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="F60" s="2">
-        <v>1.01</v>
+        <v>3.77</v>
       </c>
       <c r="G60" s="2">
-        <v>3.54</v>
+        <v>-2.27</v>
       </c>
       <c r="H60" s="2">
-        <v>-26.17</v>
+        <v>7.87</v>
       </c>
       <c r="I60" s="1">
-        <v>397891</v>
+        <v>590146</v>
       </c>
       <c r="J60" t="str">
         <v/>
@@ -2328,28 +2328,28 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Eicher Motors Limited</v>
+        <v>Indian Energy Exchange Ltd</v>
       </c>
       <c r="C61" t="str">
-        <v>EICHERMOT</v>
+        <v>IEX</v>
       </c>
       <c r="D61" s="1">
-        <v>7119</v>
+        <v>106.29</v>
       </c>
       <c r="E61" s="2">
-        <v>0.98</v>
+        <v>1.84</v>
       </c>
       <c r="F61" s="2">
-        <v>0.98</v>
+        <v>1.44</v>
       </c>
       <c r="G61" s="2">
-        <v>-0.43</v>
+        <v>-0.66</v>
       </c>
       <c r="H61" s="2">
-        <v>-2.65</v>
+        <v>-20.81</v>
       </c>
       <c r="I61" s="1">
-        <v>377241</v>
+        <v>3942152</v>
       </c>
       <c r="J61" t="str">
         <v/>
@@ -2360,28 +2360,28 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Computer Age Management Services Ltd</v>
+        <v>Ultratech Cement Limited</v>
       </c>
       <c r="C62" t="str">
-        <v>CAMS</v>
+        <v>ULTRACEMCO</v>
       </c>
       <c r="D62" s="1">
-        <v>679.05</v>
+        <v>10711</v>
       </c>
       <c r="E62" s="2">
-        <v>0.97</v>
+        <v>1.82</v>
       </c>
       <c r="F62" s="2">
-        <v>0.97</v>
+        <v>0.34</v>
       </c>
       <c r="G62" s="2">
-        <v>1.2</v>
+        <v>-2.24</v>
       </c>
       <c r="H62" s="2">
-        <v>-8.35</v>
+        <v>-9.11</v>
       </c>
       <c r="I62" s="1">
-        <v>1251064</v>
+        <v>190436</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -2392,28 +2392,28 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Waaree Energies Ltd</v>
+        <v>Colgate Palmolive (india) Limited</v>
       </c>
       <c r="C63" t="str">
-        <v>WAAREEENER</v>
+        <v>COLPAL</v>
       </c>
       <c r="D63" s="1">
-        <v>2345</v>
+        <v>1799.1</v>
       </c>
       <c r="E63" s="2">
-        <v>0.95</v>
+        <v>1.82</v>
       </c>
       <c r="F63" s="2">
-        <v>0.95</v>
+        <v>-1.03</v>
       </c>
       <c r="G63" s="2">
-        <v>-1.24</v>
+        <v>2.03</v>
       </c>
       <c r="H63" s="2">
-        <v>-20.99</v>
+        <v>-13.33</v>
       </c>
       <c r="I63" s="1">
-        <v>499868</v>
+        <v>350120</v>
       </c>
       <c r="J63" t="str">
         <v/>
@@ -2424,28 +2424,28 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>Divi's Laboratories Limited</v>
+        <v>Jio Financial Services Ltd</v>
       </c>
       <c r="C64" t="str">
-        <v>DIVISLAB</v>
+        <v>JIOFIN</v>
       </c>
       <c r="D64" s="1">
-        <v>9426</v>
+        <v>217.26</v>
       </c>
       <c r="E64" s="2">
-        <v>0.92</v>
+        <v>1.79</v>
       </c>
       <c r="F64" s="2">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="G64" s="2">
-        <v>1.45</v>
+        <v>0.18</v>
       </c>
       <c r="H64" s="2">
-        <v>47.45</v>
+        <v>-26.34</v>
       </c>
       <c r="I64" s="1">
-        <v>358499</v>
+        <v>16658093</v>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -2456,28 +2456,28 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Hero Motocorp Limited</v>
+        <v>Axis Bank Limited</v>
       </c>
       <c r="C65" t="str">
-        <v>HEROMOTOCO</v>
+        <v>AXISBANK</v>
       </c>
       <c r="D65" s="1">
-        <v>4937</v>
+        <v>1275</v>
       </c>
       <c r="E65" s="2">
-        <v>0.85</v>
+        <v>1.76</v>
       </c>
       <c r="F65" s="2">
-        <v>0.85</v>
+        <v>1.26</v>
       </c>
       <c r="G65" s="2">
-        <v>-5.8</v>
+        <v>4</v>
       </c>
       <c r="H65" s="2">
-        <v>-14.45</v>
+        <v>0.44</v>
       </c>
       <c r="I65" s="1">
-        <v>318402</v>
+        <v>5325492</v>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -2488,28 +2488,28 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Mazagon Dock Shipbuilders Ltd</v>
+        <v>Hindalco Industries Limited</v>
       </c>
       <c r="C66" t="str">
-        <v>MAZDOCK</v>
+        <v>HINDALCO</v>
       </c>
       <c r="D66" s="1">
-        <v>2027</v>
+        <v>898</v>
       </c>
       <c r="E66" s="2">
-        <v>0.85</v>
+        <v>1.76</v>
       </c>
       <c r="F66" s="2">
-        <v>0.85</v>
+        <v>-0.26</v>
       </c>
       <c r="G66" s="2">
-        <v>-4.07</v>
+        <v>-4.65</v>
       </c>
       <c r="H66" s="2">
-        <v>-18.6</v>
+        <v>1.27</v>
       </c>
       <c r="I66" s="1">
-        <v>588340</v>
+        <v>5111928</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -2520,28 +2520,28 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>Aurobindo Pharma Limited</v>
+        <v>Yes Bank Limited</v>
       </c>
       <c r="C67" t="str">
-        <v>AUROPHARMA</v>
+        <v>YESBANK</v>
       </c>
       <c r="D67" s="1">
-        <v>1706.9</v>
+        <v>20.8</v>
       </c>
       <c r="E67" s="2">
-        <v>0.82</v>
+        <v>1.76</v>
       </c>
       <c r="F67" s="2">
-        <v>0.82</v>
+        <v>1.46</v>
       </c>
       <c r="G67" s="2">
-        <v>2.09</v>
+        <v>-0.72</v>
       </c>
       <c r="H67" s="2">
-        <v>44.29</v>
+        <v>-3.7</v>
       </c>
       <c r="I67" s="1">
-        <v>1190866</v>
+        <v>61267081</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -2552,28 +2552,28 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>Cipla Limited</v>
+        <v>Amber Enterprises India Ltd</v>
       </c>
       <c r="C68" t="str">
-        <v>CIPLA</v>
+        <v>AMBER</v>
       </c>
       <c r="D68" s="1">
-        <v>1311.3</v>
+        <v>6638</v>
       </c>
       <c r="E68" s="2">
-        <v>0.79</v>
+        <v>1.69</v>
       </c>
       <c r="F68" s="2">
-        <v>0.79</v>
+        <v>2.99</v>
       </c>
       <c r="G68" s="2">
-        <v>-2.58</v>
+        <v>-0.52</v>
       </c>
       <c r="H68" s="2">
-        <v>-13.23</v>
+        <v>3.93</v>
       </c>
       <c r="I68" s="1">
-        <v>666122</v>
+        <v>131716</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -2584,28 +2584,28 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>Inox Wind Limited</v>
+        <v>Patanjali Foods Ltd</v>
       </c>
       <c r="C69" t="str">
-        <v>INOXWIND</v>
+        <v>PATANJALI</v>
       </c>
       <c r="D69" s="1">
-        <v>67.17</v>
+        <v>367.45</v>
       </c>
       <c r="E69" s="2">
-        <v>0.78</v>
+        <v>1.69</v>
       </c>
       <c r="F69" s="2">
-        <v>0.78</v>
+        <v>1.94</v>
       </c>
       <c r="G69" s="2">
-        <v>-3.37</v>
+        <v>1.23</v>
       </c>
       <c r="H69" s="2">
-        <v>-45.62</v>
+        <v>-32.64</v>
       </c>
       <c r="I69" s="1">
-        <v>12219487</v>
+        <v>1977266</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -2616,28 +2616,28 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>Force Motors Ltd</v>
+        <v>Nbcc (india) Limited</v>
       </c>
       <c r="C70" t="str">
-        <v>FORCEMOT</v>
+        <v>NBCC</v>
       </c>
       <c r="D70" s="1">
-        <v>17010</v>
+        <v>77.2</v>
       </c>
       <c r="E70" s="2">
-        <v>0.65</v>
+        <v>1.69</v>
       </c>
       <c r="F70" s="2">
-        <v>0.65</v>
+        <v>3.68</v>
       </c>
       <c r="G70" s="2">
-        <v>-0.26</v>
+        <v>-1.66</v>
       </c>
       <c r="H70" s="2">
-        <v>-17.29</v>
+        <v>-36.6</v>
       </c>
       <c r="I70" s="1">
-        <v>38264</v>
+        <v>3058380</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -2648,28 +2648,28 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>Pi Industries Limited</v>
+        <v>Upl Limited</v>
       </c>
       <c r="C71" t="str">
-        <v>PIIND</v>
+        <v>UPL</v>
       </c>
       <c r="D71" s="1">
-        <v>2131.5</v>
+        <v>523.5</v>
       </c>
       <c r="E71" s="2">
-        <v>0.63</v>
+        <v>1.68</v>
       </c>
       <c r="F71" s="2">
-        <v>0.63</v>
+        <v>7.18</v>
       </c>
       <c r="G71" s="2">
-        <v>-7.73</v>
+        <v>-3.01</v>
       </c>
       <c r="H71" s="2">
-        <v>-34.18</v>
+        <v>-34.16</v>
       </c>
       <c r="I71" s="1">
-        <v>75514</v>
+        <v>1873281</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -2680,28 +2680,28 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>Hindustan Zinc Limited</v>
+        <v>Abb India Limited</v>
       </c>
       <c r="C72" t="str">
-        <v>HINDZINC</v>
+        <v>ABB</v>
       </c>
       <c r="D72" s="1">
-        <v>546.9</v>
+        <v>6970</v>
       </c>
       <c r="E72" s="2">
-        <v>0.63</v>
+        <v>1.67</v>
       </c>
       <c r="F72" s="2">
-        <v>0.63</v>
+        <v>2.8</v>
       </c>
       <c r="G72" s="2">
-        <v>-3.37</v>
+        <v>2.86</v>
       </c>
       <c r="H72" s="2">
-        <v>-10.7</v>
+        <v>34.82</v>
       </c>
       <c r="I72" s="1">
-        <v>1953013</v>
+        <v>202398</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -2712,28 +2712,28 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>Icici Prudential Life Insurance Company Limited</v>
+        <v>Nmdc Limited</v>
       </c>
       <c r="C73" t="str">
-        <v>ICICIPRULI</v>
+        <v>NMDC</v>
       </c>
       <c r="D73" s="1">
-        <v>463.4</v>
+        <v>71.5</v>
       </c>
       <c r="E73" s="2">
-        <v>0.62</v>
+        <v>1.65</v>
       </c>
       <c r="F73" s="2">
-        <v>0.62</v>
+        <v>-0.42</v>
       </c>
       <c r="G73" s="2">
-        <v>4.42</v>
+        <v>-6.58</v>
       </c>
       <c r="H73" s="2">
-        <v>-30.65</v>
+        <v>-14.03</v>
       </c>
       <c r="I73" s="1">
-        <v>451502</v>
+        <v>11712025</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -2744,28 +2744,28 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>Mahindra &amp; Mahindra Limited</v>
+        <v>Jindal Steel Ltd</v>
       </c>
       <c r="C74" t="str">
-        <v>M&amp;M</v>
+        <v>JINDALSTEL</v>
       </c>
       <c r="D74" s="1">
-        <v>2813</v>
+        <v>1029</v>
       </c>
       <c r="E74" s="2">
-        <v>0.6</v>
+        <v>1.63</v>
       </c>
       <c r="F74" s="2">
-        <v>0.6</v>
+        <v>1.21</v>
       </c>
       <c r="G74" s="2">
-        <v>-4.64</v>
+        <v>-9.33</v>
       </c>
       <c r="H74" s="2">
-        <v>-24.16</v>
+        <v>-2.35</v>
       </c>
       <c r="I74" s="1">
-        <v>1907713</v>
+        <v>537458</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -2776,28 +2776,28 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>L&amp;T Finance Ltd</v>
+        <v>PB Fintech Ltd</v>
       </c>
       <c r="C75" t="str">
-        <v>LTF</v>
+        <v>POLICYBZR</v>
       </c>
       <c r="D75" s="1">
-        <v>262.7</v>
+        <v>1064</v>
       </c>
       <c r="E75" s="2">
-        <v>0.57</v>
+        <v>1.62</v>
       </c>
       <c r="F75" s="2">
-        <v>0.57</v>
+        <v>5.14</v>
       </c>
       <c r="G75" s="2">
-        <v>-0.87</v>
+        <v>0.01</v>
       </c>
       <c r="H75" s="2">
-        <v>-16.85</v>
+        <v>-41.72</v>
       </c>
       <c r="I75" s="1">
-        <v>2127416</v>
+        <v>3292281</v>
       </c>
       <c r="J75" t="str">
         <v/>
@@ -2808,28 +2808,28 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>Nhpc Limited</v>
+        <v>Icici Bank Limited</v>
       </c>
       <c r="C76" t="str">
-        <v>NHPC</v>
+        <v>ICICIBANK</v>
       </c>
       <c r="D76" s="1">
-        <v>73.4</v>
+        <v>1361.6</v>
       </c>
       <c r="E76" s="2">
-        <v>0.56</v>
+        <v>1.61</v>
       </c>
       <c r="F76" s="2">
-        <v>0.56</v>
+        <v>0.49</v>
       </c>
       <c r="G76" s="2">
-        <v>0.81</v>
+        <v>3.02</v>
       </c>
       <c r="H76" s="2">
-        <v>-7.35</v>
+        <v>1.39</v>
       </c>
       <c r="I76" s="1">
-        <v>4112974</v>
+        <v>5560104</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -2840,28 +2840,28 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>Supreme Industries Limited</v>
+        <v>Bharat Electronics Limited</v>
       </c>
       <c r="C77" t="str">
-        <v>SUPREMEIND</v>
+        <v>BEL</v>
       </c>
       <c r="D77" s="1">
-        <v>3493.8</v>
+        <v>379.85</v>
       </c>
       <c r="E77" s="2">
-        <v>0.55</v>
+        <v>1.59</v>
       </c>
       <c r="F77" s="2">
-        <v>0.55</v>
+        <v>3.18</v>
       </c>
       <c r="G77" s="2">
-        <v>1.24</v>
+        <v>-2.18</v>
       </c>
       <c r="H77" s="2">
-        <v>4.17</v>
+        <v>-4.94</v>
       </c>
       <c r="I77" s="1">
-        <v>218939</v>
+        <v>7792614</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -2872,28 +2872,28 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>Siemens Energy India Ltd</v>
+        <v>Voltas Limited</v>
       </c>
       <c r="C78" t="str">
-        <v>ENRIN</v>
+        <v>VOLTAS</v>
       </c>
       <c r="D78" s="1">
-        <v>3118.1</v>
+        <v>1036.1</v>
       </c>
       <c r="E78" s="2">
-        <v>0.55</v>
+        <v>1.58</v>
       </c>
       <c r="F78" s="2">
-        <v>0.55</v>
+        <v>0.23</v>
       </c>
       <c r="G78" s="2">
-        <v>-2.56</v>
+        <v>-3.17</v>
       </c>
       <c r="H78" s="2">
-        <v>21.8</v>
+        <v>-23.88</v>
       </c>
       <c r="I78" s="1">
-        <v>460048</v>
+        <v>461550</v>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -2904,28 +2904,28 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>Torrent Pharmaceuticals Limited</v>
+        <v>Suzlon Energy Limited</v>
       </c>
       <c r="C79" t="str">
-        <v>TORNTPHARM</v>
+        <v>SUZLON</v>
       </c>
       <c r="D79" s="1">
-        <v>4682</v>
+        <v>40.19</v>
       </c>
       <c r="E79" s="2">
-        <v>0.54</v>
+        <v>1.57</v>
       </c>
       <c r="F79" s="2">
-        <v>0.54</v>
+        <v>6.89</v>
       </c>
       <c r="G79" s="2">
-        <v>-2.46</v>
+        <v>1.77</v>
       </c>
       <c r="H79" s="2">
-        <v>21.61</v>
+        <v>-23.69</v>
       </c>
       <c r="I79" s="1">
-        <v>420840</v>
+        <v>82799670</v>
       </c>
       <c r="J79" t="str">
         <v/>
@@ -2936,28 +2936,28 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>Kotak Mahindra Bank Limited</v>
+        <v>The Indian Hotels Company Limited</v>
       </c>
       <c r="C80" t="str">
-        <v>KOTAKBANK</v>
+        <v>INDHOTEL</v>
       </c>
       <c r="D80" s="1">
-        <v>443.4</v>
+        <v>722.55</v>
       </c>
       <c r="E80" s="2">
-        <v>0.54</v>
+        <v>1.55</v>
       </c>
       <c r="F80" s="2">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="G80" s="2">
-        <v>6.33</v>
+        <v>-0.84</v>
       </c>
       <c r="H80" s="2">
-        <v>0.72</v>
+        <v>-2.21</v>
       </c>
       <c r="I80" s="1">
-        <v>17833238</v>
+        <v>1686567</v>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -2968,28 +2968,28 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>Hcl Technologies Limited</v>
+        <v>Manappuram Finance Limited</v>
       </c>
       <c r="C81" t="str">
-        <v>HCLTECH</v>
+        <v>MANAPPURAM</v>
       </c>
       <c r="D81" s="1">
-        <v>1223</v>
+        <v>324.95</v>
       </c>
       <c r="E81" s="2">
-        <v>0.52</v>
+        <v>1.55</v>
       </c>
       <c r="F81" s="2">
-        <v>0.52</v>
+        <v>3.22</v>
       </c>
       <c r="G81" s="2">
-        <v>-0.57</v>
+        <v>2.88</v>
       </c>
       <c r="H81" s="2">
-        <v>-24.66</v>
+        <v>5.32</v>
       </c>
       <c r="I81" s="1">
-        <v>2511247</v>
+        <v>2217436</v>
       </c>
       <c r="J81" t="str">
         <v/>
@@ -3000,28 +3000,28 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>Central Depository Services Ltd</v>
+        <v>L&amp;T Finance Ltd</v>
       </c>
       <c r="C82" t="str">
-        <v>CDSL</v>
+        <v>LTF</v>
       </c>
       <c r="D82" s="1">
-        <v>1266</v>
+        <v>266.75</v>
       </c>
       <c r="E82" s="2">
-        <v>0.48</v>
+        <v>1.54</v>
       </c>
       <c r="F82" s="2">
-        <v>0.48</v>
+        <v>2.12</v>
       </c>
       <c r="G82" s="2">
-        <v>0.16</v>
+        <v>0.66</v>
       </c>
       <c r="H82" s="2">
-        <v>-12.3</v>
+        <v>-15.57</v>
       </c>
       <c r="I82" s="1">
-        <v>750601</v>
+        <v>2233795</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -3032,28 +3032,28 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>HDFC Life Insurance Company Ltd</v>
+        <v>Titan Company Limited</v>
       </c>
       <c r="C83" t="str">
-        <v>HDFCLIFE</v>
+        <v>TITAN</v>
       </c>
       <c r="D83" s="1">
-        <v>559.25</v>
+        <v>4467.3</v>
       </c>
       <c r="E83" s="2">
-        <v>0.47</v>
+        <v>1.53</v>
       </c>
       <c r="F83" s="2">
-        <v>0.47</v>
+        <v>1.3</v>
       </c>
       <c r="G83" s="2">
-        <v>7.3</v>
+        <v>-2.61</v>
       </c>
       <c r="H83" s="2">
-        <v>-25.42</v>
+        <v>10.26</v>
       </c>
       <c r="I83" s="1">
-        <v>1704385</v>
+        <v>537528</v>
       </c>
       <c r="J83" t="str">
         <v/>
@@ -3064,28 +3064,28 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>Lodha Developers Ltd</v>
+        <v>Bharat Forge Limited</v>
       </c>
       <c r="C84" t="str">
-        <v>LODHA</v>
+        <v>BHARATFORG</v>
       </c>
       <c r="D84" s="1">
-        <v>1069.7</v>
+        <v>1843</v>
       </c>
       <c r="E84" s="2">
-        <v>0.46</v>
+        <v>1.53</v>
       </c>
       <c r="F84" s="2">
-        <v>0.46</v>
+        <v>1.44</v>
       </c>
       <c r="G84" s="2">
-        <v>-5.75</v>
+        <v>-4.31</v>
       </c>
       <c r="H84" s="2">
-        <v>0.79</v>
+        <v>25.34</v>
       </c>
       <c r="I84" s="1">
-        <v>871312</v>
+        <v>411470</v>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -3096,28 +3096,28 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>Tata Power Company Limited</v>
+        <v>NIFTY</v>
       </c>
       <c r="C85" t="str">
-        <v>TATAPOWER</v>
+        <v>NIFTY</v>
       </c>
       <c r="D85" s="1">
-        <v>343.7</v>
+        <v>22702.05</v>
       </c>
       <c r="E85" s="2">
-        <v>0.45</v>
+        <v>1.51</v>
       </c>
       <c r="F85" s="2">
-        <v>0.45</v>
+        <v>0.81</v>
       </c>
       <c r="G85" s="2">
-        <v>-4.26</v>
+        <v>0.36</v>
       </c>
       <c r="H85" s="2">
-        <v>-9.46</v>
+        <v>-13.12</v>
       </c>
       <c r="I85" s="1">
-        <v>3408910</v>
+        <v>0</v>
       </c>
       <c r="J85" t="str">
         <v/>
@@ -3128,28 +3128,28 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>Jsw Steel Limited</v>
+        <v>Mahindra &amp; Mahindra Limited</v>
       </c>
       <c r="C86" t="str">
-        <v>JSWSTEEL</v>
+        <v>M&amp;M</v>
       </c>
       <c r="D86" s="1">
-        <v>1173</v>
+        <v>2854.3</v>
       </c>
       <c r="E86" s="2">
-        <v>0.43</v>
+        <v>1.47</v>
       </c>
       <c r="F86" s="2">
-        <v>0.43</v>
+        <v>2.08</v>
       </c>
       <c r="G86" s="2">
-        <v>-6.41</v>
+        <v>-3.24</v>
       </c>
       <c r="H86" s="2">
-        <v>0.7</v>
+        <v>-23.05</v>
       </c>
       <c r="I86" s="1">
-        <v>973895</v>
+        <v>2607450</v>
       </c>
       <c r="J86" t="str">
         <v/>
@@ -3160,28 +3160,28 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>KPIT Technologies Ltd</v>
+        <v>Asian Paints Limited</v>
       </c>
       <c r="C87" t="str">
-        <v>KPITTECH</v>
+        <v>ASIANPAINT</v>
       </c>
       <c r="D87" s="1">
-        <v>481</v>
+        <v>2364.7</v>
       </c>
       <c r="E87" s="2">
-        <v>0.42</v>
+        <v>1.45</v>
       </c>
       <c r="F87" s="2">
-        <v>0.42</v>
+        <v>1.09</v>
       </c>
       <c r="G87" s="2">
-        <v>-3.63</v>
+        <v>-1.58</v>
       </c>
       <c r="H87" s="2">
-        <v>-58.98</v>
+        <v>-14.62</v>
       </c>
       <c r="I87" s="1">
-        <v>1514282</v>
+        <v>551241</v>
       </c>
       <c r="J87" t="str">
         <v/>
@@ -3192,28 +3192,28 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>TATA Consumer Products Ltd</v>
+        <v>Hdfc Bank Limited</v>
       </c>
       <c r="C88" t="str">
-        <v>TATACONSUM</v>
+        <v>HDFCBANK</v>
       </c>
       <c r="D88" s="1">
-        <v>958.8</v>
+        <v>714.95</v>
       </c>
       <c r="E88" s="2">
-        <v>0.4</v>
+        <v>1.43</v>
       </c>
       <c r="F88" s="2">
-        <v>0.4</v>
+        <v>1.09</v>
       </c>
       <c r="G88" s="2">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="H88" s="2">
-        <v>-19.56</v>
+        <v>-27.87</v>
       </c>
       <c r="I88" s="1">
-        <v>716582</v>
+        <v>17272469</v>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -3224,28 +3224,28 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>Muthoot Finance Limited</v>
+        <v>Canara Bank Ltd</v>
       </c>
       <c r="C89" t="str">
-        <v>MUTHOOTFIN</v>
+        <v>CANBK</v>
       </c>
       <c r="D89" s="1">
-        <v>2634.1</v>
+        <v>120</v>
       </c>
       <c r="E89" s="2">
-        <v>0.36</v>
+        <v>1.37</v>
       </c>
       <c r="F89" s="2">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="G89" s="2">
-        <v>-3.76</v>
+        <v>0.47</v>
       </c>
       <c r="H89" s="2">
-        <v>-30.89</v>
+        <v>-22.54</v>
       </c>
       <c r="I89" s="1">
-        <v>333177</v>
+        <v>12843428</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -3256,28 +3256,28 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>Vedanta Limited</v>
+        <v>ICICI Lombard General Insurance Company Ltd</v>
       </c>
       <c r="C90" t="str">
-        <v>VEDL</v>
+        <v>ICICIGI</v>
       </c>
       <c r="D90" s="1">
-        <v>264.9</v>
+        <v>1696.6</v>
       </c>
       <c r="E90" s="2">
-        <v>0.34</v>
+        <v>1.35</v>
       </c>
       <c r="F90" s="2">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="G90" s="2">
-        <v>2.28</v>
+        <v>6.7</v>
       </c>
       <c r="H90" s="2">
-        <v>21.15</v>
+        <v>-13.53</v>
       </c>
       <c r="I90" s="1">
-        <v>10325784</v>
+        <v>590574</v>
       </c>
       <c r="J90" t="str">
         <v/>
@@ -3288,28 +3288,28 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>REC Ltd</v>
+        <v>Biocon Limited</v>
       </c>
       <c r="C91" t="str">
-        <v>RECLTD</v>
+        <v>BIOCON</v>
       </c>
       <c r="D91" s="1">
-        <v>301</v>
+        <v>351</v>
       </c>
       <c r="E91" s="2">
-        <v>0.33</v>
+        <v>1.34</v>
       </c>
       <c r="F91" s="2">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="G91" s="2">
-        <v>0.67</v>
+        <v>-5.21</v>
       </c>
       <c r="H91" s="2">
-        <v>-15.64</v>
+        <v>-10.89</v>
       </c>
       <c r="I91" s="1">
-        <v>6909261</v>
+        <v>2351791</v>
       </c>
       <c r="J91" t="str">
         <v/>
@@ -3320,28 +3320,28 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>Bandhan Bank Ltd</v>
+        <v>Power Finance Corporation Limited</v>
       </c>
       <c r="C92" t="str">
-        <v>BANDHANBNK</v>
+        <v>PFC</v>
       </c>
       <c r="D92" s="1">
-        <v>157.5</v>
+        <v>342.4</v>
       </c>
       <c r="E92" s="2">
-        <v>0.32</v>
+        <v>1.33</v>
       </c>
       <c r="F92" s="2">
-        <v>0.32</v>
+        <v>4.45</v>
       </c>
       <c r="G92" s="2">
-        <v>-11.63</v>
+        <v>5.19</v>
       </c>
       <c r="H92" s="2">
-        <v>8.01</v>
+        <v>-3.66</v>
       </c>
       <c r="I92" s="1">
-        <v>6411439</v>
+        <v>19753244</v>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -3352,28 +3352,28 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>Persistent Systems Limited</v>
+        <v>Max Financial Services Limited</v>
       </c>
       <c r="C93" t="str">
-        <v>PERSISTENT</v>
+        <v>MFSL</v>
       </c>
       <c r="D93" s="1">
-        <v>5787</v>
+        <v>1323.7</v>
       </c>
       <c r="E93" s="2">
-        <v>0.29</v>
+        <v>1.32</v>
       </c>
       <c r="F93" s="2">
-        <v>0.29</v>
+        <v>1.07</v>
       </c>
       <c r="G93" s="2">
-        <v>9.62</v>
+        <v>-3.62</v>
       </c>
       <c r="H93" s="2">
-        <v>-7.73</v>
+        <v>-20.82</v>
       </c>
       <c r="I93" s="1">
-        <v>332431</v>
+        <v>1145931</v>
       </c>
       <c r="J93" t="str">
         <v/>
@@ -3384,28 +3384,28 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>Patanjali Foods Ltd</v>
+        <v>Nippon Life India Asset Management Ltd</v>
       </c>
       <c r="C94" t="str">
-        <v>PATANJALI</v>
+        <v>NAM-INDIA</v>
       </c>
       <c r="D94" s="1">
-        <v>361.35</v>
+        <v>1070.9</v>
       </c>
       <c r="E94" s="2">
-        <v>0.25</v>
+        <v>1.32</v>
       </c>
       <c r="F94" s="2">
-        <v>0.25</v>
+        <v>2.48</v>
       </c>
       <c r="G94" s="2">
-        <v>-0.45</v>
+        <v>0.08</v>
       </c>
       <c r="H94" s="2">
-        <v>-33.76</v>
+        <v>21.74</v>
       </c>
       <c r="I94" s="1">
-        <v>1397374</v>
+        <v>548349</v>
       </c>
       <c r="J94" t="str">
         <v/>
@@ -3416,28 +3416,28 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>Dlf Limited</v>
+        <v>State Bank Of India Ltd</v>
       </c>
       <c r="C95" t="str">
-        <v>DLF</v>
+        <v>SBIN</v>
       </c>
       <c r="D95" s="1">
-        <v>650</v>
+        <v>953.35</v>
       </c>
       <c r="E95" s="2">
-        <v>0.22</v>
+        <v>1.31</v>
       </c>
       <c r="F95" s="2">
-        <v>0.22</v>
+        <v>-0.6</v>
       </c>
       <c r="G95" s="2">
-        <v>-3.56</v>
+        <v>-0.64</v>
       </c>
       <c r="H95" s="2">
-        <v>-5.44</v>
+        <v>-2.94</v>
       </c>
       <c r="I95" s="1">
-        <v>2254441</v>
+        <v>6756140</v>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -3448,28 +3448,28 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>Indian Renewable Energy Development Agency Ltd</v>
+        <v>Swiggy Ltd</v>
       </c>
       <c r="C96" t="str">
-        <v>IREDA</v>
+        <v>SWIGGY</v>
       </c>
       <c r="D96" s="1">
-        <v>104.6</v>
+        <v>233</v>
       </c>
       <c r="E96" s="2">
-        <v>0.19</v>
+        <v>1.3</v>
       </c>
       <c r="F96" s="2">
-        <v>0.19</v>
+        <v>-0.51</v>
       </c>
       <c r="G96" s="2">
-        <v>-6.34</v>
+        <v>-6.84</v>
       </c>
       <c r="H96" s="2">
-        <v>-25.23</v>
+        <v>-39.68</v>
       </c>
       <c r="I96" s="1">
-        <v>3593549</v>
+        <v>6075689</v>
       </c>
       <c r="J96" t="str">
         <v/>
@@ -3480,28 +3480,28 @@
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>Cochin Shipyard Ltd</v>
+        <v>Adani Energy Solutions Ltd</v>
       </c>
       <c r="C97" t="str">
-        <v>COCHINSHIP</v>
+        <v>ADANIENSOL</v>
       </c>
       <c r="D97" s="1">
-        <v>1232</v>
+        <v>1296</v>
       </c>
       <c r="E97" s="2">
-        <v>0.16</v>
+        <v>1.25</v>
       </c>
       <c r="F97" s="2">
-        <v>0.16</v>
+        <v>2.69</v>
       </c>
       <c r="G97" s="2">
-        <v>-6.31</v>
+        <v>-1.41</v>
       </c>
       <c r="H97" s="2">
-        <v>-23.96</v>
+        <v>26.15</v>
       </c>
       <c r="I97" s="1">
-        <v>761099</v>
+        <v>637132</v>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -3512,28 +3512,28 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>Gail (india) Limited</v>
+        <v>BSE (Bombay stock exchange) Ltd</v>
       </c>
       <c r="C98" t="str">
-        <v>GAIL</v>
+        <v>BSE</v>
       </c>
       <c r="D98" s="1">
-        <v>166.91</v>
+        <v>3371.6</v>
       </c>
       <c r="E98" s="2">
-        <v>0.16</v>
+        <v>1.24</v>
       </c>
       <c r="F98" s="2">
-        <v>0.16</v>
+        <v>2.57</v>
       </c>
       <c r="G98" s="2">
-        <v>-2.13</v>
+        <v>9.04</v>
       </c>
       <c r="H98" s="2">
-        <v>-3.05</v>
+        <v>28.09</v>
       </c>
       <c r="I98" s="1">
-        <v>8839150</v>
+        <v>4095475</v>
       </c>
       <c r="J98" t="str">
         <v/>
@@ -3544,28 +3544,28 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>Radico Khaitan Limited</v>
+        <v>HDFC Asset Management Company Ltd</v>
       </c>
       <c r="C99" t="str">
-        <v>RADICO</v>
+        <v>HDFCAMC</v>
       </c>
       <c r="D99" s="1">
-        <v>4555</v>
+        <v>2318</v>
       </c>
       <c r="E99" s="2">
-        <v>0.11</v>
+        <v>1.24</v>
       </c>
       <c r="F99" s="2">
-        <v>0.11</v>
+        <v>2.45</v>
       </c>
       <c r="G99" s="2">
-        <v>4.33</v>
+        <v>1.64</v>
       </c>
       <c r="H99" s="2">
-        <v>38.1</v>
+        <v>-13.26</v>
       </c>
       <c r="I99" s="1">
-        <v>216671</v>
+        <v>700335</v>
       </c>
       <c r="J99" t="str">
         <v/>
@@ -3576,28 +3576,28 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>Cummins India Limited</v>
+        <v>Apollo Hospitals Enterprise Limited</v>
       </c>
       <c r="C100" t="str">
-        <v>CUMMINSIND</v>
+        <v>APOLLOHOSP</v>
       </c>
       <c r="D100" s="1">
-        <v>4835</v>
+        <v>7871</v>
       </c>
       <c r="E100" s="2">
-        <v>0.1</v>
+        <v>1.23</v>
       </c>
       <c r="F100" s="2">
-        <v>0.1</v>
+        <v>-1.95</v>
       </c>
       <c r="G100" s="2">
-        <v>1.58</v>
+        <v>-3.61</v>
       </c>
       <c r="H100" s="2">
-        <v>9.03</v>
+        <v>11.76</v>
       </c>
       <c r="I100" s="1">
-        <v>274337</v>
+        <v>462999</v>
       </c>
       <c r="J100" t="str">
         <v/>
@@ -3608,28 +3608,28 @@
         <v>100</v>
       </c>
       <c r="B101" t="str">
-        <v>Page Industries Limited</v>
+        <v>Tata Steel Limited</v>
       </c>
       <c r="C101" t="str">
-        <v>PAGEIND</v>
+        <v>TATASTEEL</v>
       </c>
       <c r="D101" s="1">
-        <v>36905</v>
+        <v>174.36</v>
       </c>
       <c r="E101" s="2">
-        <v>0.08</v>
+        <v>1.23</v>
       </c>
       <c r="F101" s="2">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="G101" s="2">
-        <v>1.43</v>
+        <v>-5.39</v>
       </c>
       <c r="H101" s="2">
-        <v>2.39</v>
+        <v>-3.18</v>
       </c>
       <c r="I101" s="1">
-        <v>6358</v>
+        <v>20019314</v>
       </c>
       <c r="J101" t="str">
         <v/>
@@ -3640,28 +3640,28 @@
         <v>101</v>
       </c>
       <c r="B102" t="str">
-        <v>Oberoi Realty Limited</v>
+        <v>Itc Limited</v>
       </c>
       <c r="C102" t="str">
-        <v>OBEROIRLTY</v>
+        <v>ITC</v>
       </c>
       <c r="D102" s="1">
-        <v>1700</v>
+        <v>261.05</v>
       </c>
       <c r="E102" s="2">
-        <v>0.07</v>
+        <v>1.22</v>
       </c>
       <c r="F102" s="2">
-        <v>0.07</v>
+        <v>-1.86</v>
       </c>
       <c r="G102" s="2">
-        <v>-3.72</v>
+        <v>-0.65</v>
       </c>
       <c r="H102" s="2">
-        <v>1.76</v>
+        <v>-35.22</v>
       </c>
       <c r="I102" s="1">
-        <v>402957</v>
+        <v>13039772</v>
       </c>
       <c r="J102" t="str">
         <v/>
@@ -3672,28 +3672,28 @@
         <v>102</v>
       </c>
       <c r="B103" t="str">
-        <v>Hyundai Motor India Ltd</v>
+        <v>Larsen &amp; Toubro Limited</v>
       </c>
       <c r="C103" t="str">
-        <v>HYUNDAI</v>
+        <v>LT</v>
       </c>
       <c r="D103" s="1">
-        <v>1941.1</v>
+        <v>3671.2</v>
       </c>
       <c r="E103" s="2">
-        <v>0.06</v>
+        <v>1.2</v>
       </c>
       <c r="F103" s="2">
-        <v>0.06</v>
+        <v>-0.87</v>
       </c>
       <c r="G103" s="2">
-        <v>-4.43</v>
+        <v>-2.36</v>
       </c>
       <c r="H103" s="2">
-        <v>-15.53</v>
+        <v>-10.1</v>
       </c>
       <c r="I103" s="1">
-        <v>364329</v>
+        <v>2180217</v>
       </c>
       <c r="J103" t="str">
         <v/>
@@ -3704,28 +3704,28 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>Tube Investments of India Ltd</v>
+        <v>AU Small Finance Bank Ltd</v>
       </c>
       <c r="C104" t="str">
-        <v>TIINDIA</v>
+        <v>AUBANK</v>
       </c>
       <c r="D104" s="1">
-        <v>2214</v>
+        <v>988.5</v>
       </c>
       <c r="E104" s="2">
-        <v>0.05</v>
+        <v>1.16</v>
       </c>
       <c r="F104" s="2">
-        <v>0.05</v>
+        <v>0.66</v>
       </c>
       <c r="G104" s="2">
-        <v>-6.78</v>
+        <v>-2.16</v>
       </c>
       <c r="H104" s="2">
-        <v>-15.31</v>
+        <v>-0.6</v>
       </c>
       <c r="I104" s="1">
-        <v>659603</v>
+        <v>1178883</v>
       </c>
       <c r="J104" t="str">
         <v/>
@@ -3736,28 +3736,28 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>Sun Pharmaceuticals Industries Limited</v>
+        <v>Steel Authority Of India Limited</v>
       </c>
       <c r="C105" t="str">
-        <v>SUNPHARMA</v>
+        <v>SAIL</v>
       </c>
       <c r="D105" s="1">
-        <v>1760</v>
+        <v>172.99</v>
       </c>
       <c r="E105" s="2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="F105" s="2">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="G105" s="2">
-        <v>-3.12</v>
+        <v>-4.68</v>
       </c>
       <c r="H105" s="2">
-        <v>2.34</v>
+        <v>17.69</v>
       </c>
       <c r="I105" s="1">
-        <v>1141685</v>
+        <v>12124129</v>
       </c>
       <c r="J105" t="str">
         <v/>
@@ -3768,28 +3768,28 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>Power Grid Corporation Of India Limited</v>
+        <v>Oberoi Realty Limited</v>
       </c>
       <c r="C106" t="str">
-        <v>POWERGRID</v>
+        <v>OBEROIRLTY</v>
       </c>
       <c r="D106" s="1">
-        <v>249</v>
+        <v>1719</v>
       </c>
       <c r="E106" s="2">
-        <v>-0.06</v>
+        <v>1.12</v>
       </c>
       <c r="F106" s="2">
-        <v>-0.06</v>
+        <v>1.19</v>
       </c>
       <c r="G106" s="2">
-        <v>-4.41</v>
+        <v>-2.64</v>
       </c>
       <c r="H106" s="2">
-        <v>-5.9</v>
+        <v>2.9</v>
       </c>
       <c r="I106" s="1">
-        <v>6205671</v>
+        <v>540782</v>
       </c>
       <c r="J106" t="str">
         <v/>
@@ -3800,28 +3800,28 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>Rbl Bank Limited</v>
+        <v>Shree Cements Limited</v>
       </c>
       <c r="C107" t="str">
-        <v>RBLBANK</v>
+        <v>SHREECEM</v>
       </c>
       <c r="D107" s="1">
-        <v>417.7</v>
+        <v>22100</v>
       </c>
       <c r="E107" s="2">
-        <v>-0.07</v>
+        <v>1.1</v>
       </c>
       <c r="F107" s="2">
-        <v>-0.07</v>
+        <v>0.09</v>
       </c>
       <c r="G107" s="2">
-        <v>3.56</v>
+        <v>-1.1</v>
       </c>
       <c r="H107" s="2">
-        <v>32.27</v>
+        <v>-16.84</v>
       </c>
       <c r="I107" s="1">
-        <v>3453163</v>
+        <v>18689</v>
       </c>
       <c r="J107" t="str">
         <v/>
@@ -3832,28 +3832,28 @@
         <v>107</v>
       </c>
       <c r="B108" t="str">
-        <v>Bharat Forge Limited</v>
+        <v>Info Edge (india) Limited</v>
       </c>
       <c r="C108" t="str">
-        <v>BHARATFORG</v>
+        <v>NAUKRI</v>
       </c>
       <c r="D108" s="1">
-        <v>1815.3</v>
+        <v>1217</v>
       </c>
       <c r="E108" s="2">
-        <v>-0.09</v>
+        <v>1.09</v>
       </c>
       <c r="F108" s="2">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="G108" s="2">
-        <v>-5.75</v>
+        <v>-0.21</v>
       </c>
       <c r="H108" s="2">
-        <v>23.46</v>
+        <v>-8.74</v>
       </c>
       <c r="I108" s="1">
-        <v>1189319</v>
+        <v>1462163</v>
       </c>
       <c r="J108" t="str">
         <v/>
@@ -3864,28 +3864,28 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>IDFC First Bank Ltd</v>
+        <v>360 ONE WAM Ltd</v>
       </c>
       <c r="C109" t="str">
-        <v>IDFCFIRSTB</v>
+        <v>360ONE</v>
       </c>
       <c r="D109" s="1">
-        <v>79.44</v>
+        <v>1080</v>
       </c>
       <c r="E109" s="2">
-        <v>-0.1</v>
+        <v>1.06</v>
       </c>
       <c r="F109" s="2">
-        <v>-0.1</v>
+        <v>3.05</v>
       </c>
       <c r="G109" s="2">
-        <v>-2.46</v>
+        <v>4.85</v>
       </c>
       <c r="H109" s="2">
-        <v>-7.21</v>
+        <v>-9.24</v>
       </c>
       <c r="I109" s="1">
-        <v>14611979</v>
+        <v>430768</v>
       </c>
       <c r="J109" t="str">
         <v/>
@@ -3896,28 +3896,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="str">
-        <v>Aditya Birla Capital Ltd</v>
+        <v>One 97 Communications Ltd</v>
       </c>
       <c r="C110" t="str">
-        <v>ABCAPITAL</v>
+        <v>PAYTM</v>
       </c>
       <c r="D110" s="1">
-        <v>380.25</v>
+        <v>1707.7</v>
       </c>
       <c r="E110" s="2">
-        <v>-0.12</v>
+        <v>1.05</v>
       </c>
       <c r="F110" s="2">
-        <v>-0.12</v>
+        <v>4.38</v>
       </c>
       <c r="G110" s="2">
-        <v>-0.09</v>
+        <v>1.77</v>
       </c>
       <c r="H110" s="2">
-        <v>6.3</v>
+        <v>31.47</v>
       </c>
       <c r="I110" s="1">
-        <v>3567322</v>
+        <v>9205329</v>
       </c>
       <c r="J110" t="str">
         <v/>
@@ -3928,28 +3928,28 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>Eternal Ltd</v>
+        <v>Bharti Airtel Limited</v>
       </c>
       <c r="C111" t="str">
-        <v>ETERNAL</v>
+        <v>BHARTIARTL</v>
       </c>
       <c r="D111" s="1">
-        <v>323</v>
+        <v>1797.2</v>
       </c>
       <c r="E111" s="2">
-        <v>-0.14</v>
+        <v>1.04</v>
       </c>
       <c r="F111" s="2">
-        <v>-0.14</v>
+        <v>-0.44</v>
       </c>
       <c r="G111" s="2">
-        <v>0.94</v>
+        <v>2.29</v>
       </c>
       <c r="H111" s="2">
-        <v>16.17</v>
+        <v>-14.65</v>
       </c>
       <c r="I111" s="1">
-        <v>12225670</v>
+        <v>5691966</v>
       </c>
       <c r="J111" t="str">
         <v/>
@@ -3960,28 +3960,28 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>Adani Enterprises Limited</v>
+        <v>Cipla Limited</v>
       </c>
       <c r="C112" t="str">
-        <v>ADANIENT</v>
+        <v>CIPLA</v>
       </c>
       <c r="D112" s="1">
-        <v>2630</v>
+        <v>1325</v>
       </c>
       <c r="E112" s="2">
-        <v>-0.17</v>
+        <v>1.04</v>
       </c>
       <c r="F112" s="2">
-        <v>-0.17</v>
+        <v>1.84</v>
       </c>
       <c r="G112" s="2">
-        <v>-9.42</v>
+        <v>-1.56</v>
       </c>
       <c r="H112" s="2">
-        <v>17.43</v>
+        <v>-12.33</v>
       </c>
       <c r="I112" s="1">
-        <v>1112869</v>
+        <v>438625</v>
       </c>
       <c r="J112" t="str">
         <v/>
@@ -3992,28 +3992,28 @@
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>Bank Of Baroda Ltd</v>
+        <v>Dabur India Limited</v>
       </c>
       <c r="C113" t="str">
-        <v>BANKBARODA</v>
+        <v>DABUR</v>
       </c>
       <c r="D113" s="1">
-        <v>235.4</v>
+        <v>378.2</v>
       </c>
       <c r="E113" s="2">
-        <v>-0.17</v>
+        <v>1.02</v>
       </c>
       <c r="F113" s="2">
-        <v>-0.17</v>
+        <v>-2.2</v>
       </c>
       <c r="G113" s="2">
-        <v>2.1</v>
+        <v>-0.5</v>
       </c>
       <c r="H113" s="2">
-        <v>-20.45</v>
+        <v>-24.9</v>
       </c>
       <c r="I113" s="1">
-        <v>3198227</v>
+        <v>1007092</v>
       </c>
       <c r="J113" t="str">
         <v/>
@@ -4024,28 +4024,28 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>Trent Limited</v>
+        <v>Delhivery Ltd</v>
       </c>
       <c r="C114" t="str">
-        <v>TRENT</v>
+        <v>DELHIVERY</v>
       </c>
       <c r="D114" s="1">
-        <v>2913</v>
+        <v>416.3</v>
       </c>
       <c r="E114" s="2">
-        <v>-0.18</v>
+        <v>1.01</v>
       </c>
       <c r="F114" s="2">
-        <v>-0.18</v>
+        <v>3.95</v>
       </c>
       <c r="G114" s="2">
-        <v>11.12</v>
+        <v>1.61</v>
       </c>
       <c r="H114" s="2">
-        <v>2.11</v>
+        <v>3.08</v>
       </c>
       <c r="I114" s="1">
-        <v>636494</v>
+        <v>1807776</v>
       </c>
       <c r="J114" t="str">
         <v/>
@@ -4056,28 +4056,28 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>Bank Of Maharashtra Ltd</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C115" t="str">
-        <v>MAHABANK</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D115" s="1">
-        <v>83</v>
+        <v>55465.65</v>
       </c>
       <c r="E115" s="2">
-        <v>-0.19</v>
+        <v>1</v>
       </c>
       <c r="F115" s="2">
-        <v>-0.19</v>
+        <v>0.38</v>
       </c>
       <c r="G115" s="2">
-        <v>4.57</v>
+        <v>1.52</v>
       </c>
       <c r="H115" s="2">
-        <v>33.76</v>
+        <v>-6.91</v>
       </c>
       <c r="I115" s="1">
-        <v>10916983</v>
+        <v>0</v>
       </c>
       <c r="J115" t="str">
         <v/>
@@ -4088,28 +4088,28 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>Titan Company Limited</v>
+        <v>Punjab National Bank Ltd</v>
       </c>
       <c r="C116" t="str">
-        <v>TITAN</v>
+        <v>PNB</v>
       </c>
       <c r="D116" s="1">
-        <v>4400</v>
+        <v>117.11</v>
       </c>
       <c r="E116" s="2">
-        <v>-0.23</v>
+        <v>0.96</v>
       </c>
       <c r="F116" s="2">
-        <v>-0.23</v>
+        <v>0.11</v>
       </c>
       <c r="G116" s="2">
-        <v>-4.08</v>
+        <v>3.58</v>
       </c>
       <c r="H116" s="2">
-        <v>8.6</v>
+        <v>-5.24</v>
       </c>
       <c r="I116" s="1">
-        <v>724353</v>
+        <v>10377335</v>
       </c>
       <c r="J116" t="str">
         <v/>
@@ -4120,28 +4120,28 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>SBI Life Insurance Company Ltd</v>
+        <v>Coal India Limited</v>
       </c>
       <c r="C117" t="str">
-        <v>SBILIFE</v>
+        <v>COALINDIA</v>
       </c>
       <c r="D117" s="1">
-        <v>1680.8</v>
+        <v>408.65</v>
       </c>
       <c r="E117" s="2">
-        <v>-0.23</v>
+        <v>0.95</v>
       </c>
       <c r="F117" s="2">
-        <v>-0.23</v>
+        <v>-0.7</v>
       </c>
       <c r="G117" s="2">
-        <v>-0.92</v>
+        <v>-3.85</v>
       </c>
       <c r="H117" s="2">
-        <v>-17.4</v>
+        <v>2.42</v>
       </c>
       <c r="I117" s="1">
-        <v>809692</v>
+        <v>4387494</v>
       </c>
       <c r="J117" t="str">
         <v/>
@@ -4152,28 +4152,28 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>Max Financial Services Limited</v>
+        <v>Gail (india) Limited</v>
       </c>
       <c r="C118" t="str">
-        <v>MFSL</v>
+        <v>GAIL</v>
       </c>
       <c r="D118" s="1">
-        <v>1306.5</v>
+        <v>168.5</v>
       </c>
       <c r="E118" s="2">
-        <v>-0.24</v>
+        <v>0.95</v>
       </c>
       <c r="F118" s="2">
-        <v>-0.24</v>
+        <v>1.12</v>
       </c>
       <c r="G118" s="2">
-        <v>-4.87</v>
+        <v>-1.2</v>
       </c>
       <c r="H118" s="2">
-        <v>-21.85</v>
+        <v>-2.13</v>
       </c>
       <c r="I118" s="1">
-        <v>442492</v>
+        <v>7589169</v>
       </c>
       <c r="J118" t="str">
         <v/>
@@ -4184,28 +4184,28 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>Blue Star Limited</v>
+        <v>Force Motors Ltd</v>
       </c>
       <c r="C119" t="str">
-        <v>BLUESTARCO</v>
+        <v>FORCEMOT</v>
       </c>
       <c r="D119" s="1">
-        <v>1570</v>
+        <v>17170</v>
       </c>
       <c r="E119" s="2">
-        <v>-0.25</v>
+        <v>0.94</v>
       </c>
       <c r="F119" s="2">
-        <v>-0.25</v>
+        <v>1.6</v>
       </c>
       <c r="G119" s="2">
-        <v>3.43</v>
+        <v>0.68</v>
       </c>
       <c r="H119" s="2">
-        <v>-9.29</v>
+        <v>-16.51</v>
       </c>
       <c r="I119" s="1">
-        <v>190203</v>
+        <v>53496</v>
       </c>
       <c r="J119" t="str">
         <v/>
@@ -4216,28 +4216,28 @@
         <v>119</v>
       </c>
       <c r="B120" t="str">
-        <v>Mphasis Limited</v>
+        <v>Oil &amp; Natural Gas Corporation Limited</v>
       </c>
       <c r="C120" t="str">
-        <v>MPHASIS</v>
+        <v>ONGC</v>
       </c>
       <c r="D120" s="1">
-        <v>2353.5</v>
+        <v>222.06</v>
       </c>
       <c r="E120" s="2">
-        <v>-0.28</v>
+        <v>0.94</v>
       </c>
       <c r="F120" s="2">
-        <v>-0.28</v>
+        <v>0.36</v>
       </c>
       <c r="G120" s="2">
-        <v>9.24</v>
+        <v>-1.66</v>
       </c>
       <c r="H120" s="2">
-        <v>-15.68</v>
+        <v>-7.62</v>
       </c>
       <c r="I120" s="1">
-        <v>363812</v>
+        <v>5753443</v>
       </c>
       <c r="J120" t="str">
         <v/>
@@ -4248,28 +4248,28 @@
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>Container Corporation Of India Limited</v>
+        <v>Bosch Limited</v>
       </c>
       <c r="C121" t="str">
-        <v>CONCOR</v>
+        <v>BOSCHLTD</v>
       </c>
       <c r="D121" s="1">
-        <v>440.75</v>
+        <v>44995</v>
       </c>
       <c r="E121" s="2">
-        <v>-0.28</v>
+        <v>0.92</v>
       </c>
       <c r="F121" s="2">
-        <v>-0.28</v>
+        <v>3.33</v>
       </c>
       <c r="G121" s="2">
-        <v>-1.51</v>
+        <v>-4.47</v>
       </c>
       <c r="H121" s="2">
-        <v>-16.04</v>
+        <v>24.85</v>
       </c>
       <c r="I121" s="1">
-        <v>389985</v>
+        <v>16182</v>
       </c>
       <c r="J121" t="str">
         <v/>
@@ -4280,28 +4280,28 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>Pidilite Industries Limited</v>
+        <v>Aditya Birla Capital Ltd</v>
       </c>
       <c r="C122" t="str">
-        <v>PIDILITIND</v>
+        <v>ABCAPITAL</v>
       </c>
       <c r="D122" s="1">
-        <v>1477.7</v>
+        <v>383.75</v>
       </c>
       <c r="E122" s="2">
-        <v>-0.29</v>
+        <v>0.92</v>
       </c>
       <c r="F122" s="2">
-        <v>-0.29</v>
+        <v>0.8</v>
       </c>
       <c r="G122" s="2">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="H122" s="2">
-        <v>-0.32</v>
+        <v>7.28</v>
       </c>
       <c r="I122" s="1">
-        <v>533424</v>
+        <v>4153235</v>
       </c>
       <c r="J122" t="str">
         <v/>
@@ -4312,28 +4312,28 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>Bajaj Finance Limited</v>
+        <v>Life Insurance Corporation of India Ltd</v>
       </c>
       <c r="C123" t="str">
-        <v>BAJFINANCE</v>
+        <v>LICI</v>
       </c>
       <c r="D123" s="1">
-        <v>957.25</v>
+        <v>395.05</v>
       </c>
       <c r="E123" s="2">
-        <v>-0.29</v>
+        <v>0.91</v>
       </c>
       <c r="F123" s="2">
-        <v>-0.29</v>
+        <v>0.2</v>
       </c>
       <c r="G123" s="2">
-        <v>-0.22</v>
+        <v>-0.04</v>
       </c>
       <c r="H123" s="2">
-        <v>-2.99</v>
+        <v>-7.58</v>
       </c>
       <c r="I123" s="1">
-        <v>5044925</v>
+        <v>4713795</v>
       </c>
       <c r="J123" t="str">
         <v/>
@@ -4344,28 +4344,28 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>Yes Bank Limited</v>
+        <v>Dr. Reddy's Laboratories Limited</v>
       </c>
       <c r="C124" t="str">
-        <v>YESBANK</v>
+        <v>DRREDDY</v>
       </c>
       <c r="D124" s="1">
-        <v>20.44</v>
+        <v>1240.5</v>
       </c>
       <c r="E124" s="2">
-        <v>-0.29</v>
+        <v>0.9</v>
       </c>
       <c r="F124" s="2">
-        <v>-0.29</v>
+        <v>3.63</v>
       </c>
       <c r="G124" s="2">
+        <v>0.61</v>
+      </c>
+      <c r="H124" s="2">
         <v>-2.43</v>
       </c>
-      <c r="H124" s="2">
-        <v>-5.37</v>
-      </c>
       <c r="I124" s="1">
-        <v>53091781</v>
+        <v>2382940</v>
       </c>
       <c r="J124" t="str">
         <v/>
@@ -4376,28 +4376,28 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>Uno Minda Ltd</v>
+        <v>Hyundai Motor India Ltd</v>
       </c>
       <c r="C125" t="str">
-        <v>UNOMINDA</v>
+        <v>HYUNDAI</v>
       </c>
       <c r="D125" s="1">
-        <v>1104.4</v>
+        <v>1958.4</v>
       </c>
       <c r="E125" s="2">
-        <v>-0.32</v>
+        <v>0.89</v>
       </c>
       <c r="F125" s="2">
-        <v>-0.32</v>
+        <v>0.95</v>
       </c>
       <c r="G125" s="2">
-        <v>-5.61</v>
+        <v>-3.57</v>
       </c>
       <c r="H125" s="2">
-        <v>-14.11</v>
+        <v>-14.78</v>
       </c>
       <c r="I125" s="1">
-        <v>381312</v>
+        <v>775941</v>
       </c>
       <c r="J125" t="str">
         <v/>
@@ -4408,28 +4408,28 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>Steel Authority Of India Limited</v>
+        <v>GMR Airports Ltd</v>
       </c>
       <c r="C126" t="str">
-        <v>SAIL</v>
+        <v>GMRAIRPORT</v>
       </c>
       <c r="D126" s="1">
-        <v>171</v>
+        <v>90.3</v>
       </c>
       <c r="E126" s="2">
-        <v>-0.32</v>
+        <v>0.89</v>
       </c>
       <c r="F126" s="2">
-        <v>-0.32</v>
+        <v>-2.18</v>
       </c>
       <c r="G126" s="2">
-        <v>-5.78</v>
+        <v>-5.1</v>
       </c>
       <c r="H126" s="2">
-        <v>16.33</v>
+        <v>-13.48</v>
       </c>
       <c r="I126" s="1">
-        <v>27545534</v>
+        <v>13214896</v>
       </c>
       <c r="J126" t="str">
         <v/>
@@ -4440,28 +4440,28 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>Infosys Limited</v>
+        <v>Lupin Limited</v>
       </c>
       <c r="C127" t="str">
-        <v>INFY</v>
+        <v>LUPIN</v>
       </c>
       <c r="D127" s="1">
-        <v>1020</v>
+        <v>1952</v>
       </c>
       <c r="E127" s="2">
-        <v>-0.33</v>
+        <v>0.88</v>
       </c>
       <c r="F127" s="2">
-        <v>-0.33</v>
+        <v>-0.23</v>
       </c>
       <c r="G127" s="2">
-        <v>2.61</v>
+        <v>-3.85</v>
       </c>
       <c r="H127" s="2">
-        <v>-36.86</v>
+        <v>-7.47</v>
       </c>
       <c r="I127" s="1">
-        <v>8429312</v>
+        <v>705770</v>
       </c>
       <c r="J127" t="str">
         <v/>
@@ -4472,28 +4472,28 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>Hdfc Bank Limited</v>
+        <v>Hero Motocorp Limited</v>
       </c>
       <c r="C128" t="str">
-        <v>HDFCBANK</v>
+        <v>HEROMOTOCO</v>
       </c>
       <c r="D128" s="1">
-        <v>704.9</v>
+        <v>4980</v>
       </c>
       <c r="E128" s="2">
-        <v>-0.33</v>
+        <v>0.87</v>
       </c>
       <c r="F128" s="2">
-        <v>-0.33</v>
+        <v>1.73</v>
       </c>
       <c r="G128" s="2">
-        <v>-0.54</v>
+        <v>-4.98</v>
       </c>
       <c r="H128" s="2">
-        <v>-28.88</v>
+        <v>-13.71</v>
       </c>
       <c r="I128" s="1">
-        <v>18197879</v>
+        <v>405369</v>
       </c>
       <c r="J128" t="str">
         <v/>
@@ -4504,28 +4504,28 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>Petronet Lng Limited</v>
+        <v>Vodafone Idea Ltd</v>
       </c>
       <c r="C129" t="str">
-        <v>PETRONET</v>
+        <v>IDEA</v>
       </c>
       <c r="D129" s="1">
-        <v>290.5</v>
+        <v>12.78</v>
       </c>
       <c r="E129" s="2">
-        <v>-0.34</v>
+        <v>0.87</v>
       </c>
       <c r="F129" s="2">
-        <v>-0.34</v>
+        <v>-1.69</v>
       </c>
       <c r="G129" s="2">
-        <v>2.11</v>
+        <v>-1.31</v>
       </c>
       <c r="H129" s="2">
-        <v>2.25</v>
+        <v>18.77</v>
       </c>
       <c r="I129" s="1">
-        <v>1341069</v>
+        <v>240809731</v>
       </c>
       <c r="J129" t="str">
         <v/>
@@ -4536,28 +4536,28 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>Asian Paints Limited</v>
+        <v>Anand Rathi Wealth Ltd</v>
       </c>
       <c r="C130" t="str">
-        <v>ASIANPAINT</v>
+        <v>ANANDRATHI</v>
       </c>
       <c r="D130" s="1">
-        <v>2331</v>
+        <v>2105</v>
       </c>
       <c r="E130" s="2">
-        <v>-0.35</v>
+        <v>0.86</v>
       </c>
       <c r="F130" s="2">
-        <v>-0.35</v>
+        <v>3.25</v>
       </c>
       <c r="G130" s="2">
-        <v>-2.98</v>
+        <v>-0.71</v>
       </c>
       <c r="H130" s="2">
-        <v>-15.83</v>
+        <v>35.27</v>
       </c>
       <c r="I130" s="1">
-        <v>396380</v>
+        <v>242680</v>
       </c>
       <c r="J130" t="str">
         <v/>
@@ -4568,28 +4568,28 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>Godrej Properties Limited</v>
+        <v>Bank Of Baroda Ltd</v>
       </c>
       <c r="C131" t="str">
-        <v>GODREJPROP</v>
+        <v>BANKBARODA</v>
       </c>
       <c r="D131" s="1">
-        <v>1544.5</v>
+        <v>237.4</v>
       </c>
       <c r="E131" s="2">
-        <v>-0.35</v>
+        <v>0.85</v>
       </c>
       <c r="F131" s="2">
-        <v>-0.35</v>
+        <v>0.68</v>
       </c>
       <c r="G131" s="2">
-        <v>-5.16</v>
+        <v>2.97</v>
       </c>
       <c r="H131" s="2">
-        <v>-22.94</v>
+        <v>-19.77</v>
       </c>
       <c r="I131" s="1">
-        <v>292802</v>
+        <v>3698162</v>
       </c>
       <c r="J131" t="str">
         <v/>
@@ -4600,28 +4600,28 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>Indian Energy Exchange Ltd</v>
+        <v>Apl Apollo Tubes Limited</v>
       </c>
       <c r="C132" t="str">
-        <v>IEX</v>
+        <v>APLAPOLLO</v>
       </c>
       <c r="D132" s="1">
-        <v>104.37</v>
+        <v>2175</v>
       </c>
       <c r="E132" s="2">
-        <v>-0.39</v>
+        <v>0.82</v>
       </c>
       <c r="F132" s="2">
-        <v>-0.39</v>
+        <v>2.88</v>
       </c>
       <c r="G132" s="2">
-        <v>-2.46</v>
+        <v>-0.69</v>
       </c>
       <c r="H132" s="2">
-        <v>-22.24</v>
+        <v>13.64</v>
       </c>
       <c r="I132" s="1">
-        <v>3305238</v>
+        <v>302322</v>
       </c>
       <c r="J132" t="str">
         <v/>
@@ -4632,28 +4632,28 @@
         <v>132</v>
       </c>
       <c r="B133" t="str">
-        <v>Adani Ports And Special Economic Zone Limited</v>
+        <v>Astral Ltd</v>
       </c>
       <c r="C133" t="str">
-        <v>ADANIPORTS</v>
+        <v>ASTRAL</v>
       </c>
       <c r="D133" s="1">
-        <v>1754</v>
+        <v>1441.9</v>
       </c>
       <c r="E133" s="2">
-        <v>-0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F133" s="2">
-        <v>-0.4</v>
+        <v>2.28</v>
       </c>
       <c r="G133" s="2">
-        <v>-2.46</v>
+        <v>5.22</v>
       </c>
       <c r="H133" s="2">
-        <v>19.34</v>
+        <v>3.85</v>
       </c>
       <c r="I133" s="1">
-        <v>10901705</v>
+        <v>261074</v>
       </c>
       <c r="J133" t="str">
         <v/>
@@ -4664,28 +4664,28 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>Jindal Steel Ltd</v>
+        <v>United Spirits Ltd</v>
       </c>
       <c r="C134" t="str">
-        <v>JINDALSTEL</v>
+        <v>UNITDSPR</v>
       </c>
       <c r="D134" s="1">
-        <v>1012.5</v>
+        <v>1360.4</v>
       </c>
       <c r="E134" s="2">
-        <v>-0.41</v>
+        <v>0.79</v>
       </c>
       <c r="F134" s="2">
         <v>-0.41</v>
       </c>
       <c r="G134" s="2">
-        <v>-10.79</v>
+        <v>0.47</v>
       </c>
       <c r="H134" s="2">
-        <v>-3.92</v>
+        <v>-5.77</v>
       </c>
       <c r="I134" s="1">
-        <v>1274101</v>
+        <v>745500</v>
       </c>
       <c r="J134" t="str">
         <v/>
@@ -4696,28 +4696,28 @@
         <v>134</v>
       </c>
       <c r="B135" t="str">
-        <v>Cholamandalam Investment And Finance Company Limited</v>
+        <v>Sona BLW Precision Forgings Ltd</v>
       </c>
       <c r="C135" t="str">
-        <v>CHOLAFIN</v>
+        <v>SONACOMS</v>
       </c>
       <c r="D135" s="1">
-        <v>1580.7</v>
+        <v>804.3</v>
       </c>
       <c r="E135" s="2">
-        <v>-0.43</v>
+        <v>0.79</v>
       </c>
       <c r="F135" s="2">
-        <v>-0.43</v>
+        <v>2.68</v>
       </c>
       <c r="G135" s="2">
-        <v>-2.43</v>
+        <v>-3.1</v>
       </c>
       <c r="H135" s="2">
-        <v>-7.14</v>
+        <v>67.77</v>
       </c>
       <c r="I135" s="1">
-        <v>1163686</v>
+        <v>1992044</v>
       </c>
       <c r="J135" t="str">
         <v/>
@@ -4728,28 +4728,28 @@
         <v>135</v>
       </c>
       <c r="B136" t="str">
-        <v>Glenmark Pharmaceuticals Limited</v>
+        <v>Bharat Petroleum Corporation Limited</v>
       </c>
       <c r="C136" t="str">
-        <v>GLENMARK</v>
+        <v>BPCL</v>
       </c>
       <c r="D136" s="1">
-        <v>2283</v>
+        <v>286.75</v>
       </c>
       <c r="E136" s="2">
-        <v>-0.44</v>
+        <v>0.79</v>
       </c>
       <c r="F136" s="2">
-        <v>-0.44</v>
+        <v>-0.36</v>
       </c>
       <c r="G136" s="2">
-        <v>-2.21</v>
+        <v>-5.43</v>
       </c>
       <c r="H136" s="2">
-        <v>12.18</v>
+        <v>-25.33</v>
       </c>
       <c r="I136" s="1">
-        <v>695528</v>
+        <v>1699748</v>
       </c>
       <c r="J136" t="str">
         <v/>
@@ -4760,28 +4760,28 @@
         <v>136</v>
       </c>
       <c r="B137" t="str">
-        <v>Oil India Limited</v>
+        <v>Vishal Mega Mart Ltd</v>
       </c>
       <c r="C137" t="str">
-        <v>OIL</v>
+        <v>VMM</v>
       </c>
       <c r="D137" s="1">
-        <v>441.55</v>
+        <v>97.06</v>
       </c>
       <c r="E137" s="2">
-        <v>-0.44</v>
+        <v>0.79</v>
       </c>
       <c r="F137" s="2">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="G137" s="2">
-        <v>-1.58</v>
+        <v>-3.9</v>
       </c>
       <c r="H137" s="2">
-        <v>4.05</v>
+        <v>-28.83</v>
       </c>
       <c r="I137" s="1">
-        <v>1029528</v>
+        <v>6783964</v>
       </c>
       <c r="J137" t="str">
         <v/>
@@ -4792,28 +4792,28 @@
         <v>137</v>
       </c>
       <c r="B138" t="str">
-        <v>Wipro Limited</v>
+        <v>Reliance Industries Limited</v>
       </c>
       <c r="C138" t="str">
-        <v>WIPRO</v>
+        <v>RELIANCE</v>
       </c>
       <c r="D138" s="1">
-        <v>161.8</v>
+        <v>1167.8</v>
       </c>
       <c r="E138" s="2">
-        <v>-0.47</v>
+        <v>0.77</v>
       </c>
       <c r="F138" s="2">
-        <v>-0.47</v>
+        <v>-0.21</v>
       </c>
       <c r="G138" s="2">
-        <v>2.08</v>
+        <v>-1.62</v>
       </c>
       <c r="H138" s="2">
-        <v>-38.54</v>
+        <v>-25.64</v>
       </c>
       <c r="I138" s="1">
-        <v>6207783</v>
+        <v>10587951</v>
       </c>
       <c r="J138" t="str">
         <v/>
@@ -4824,28 +4824,28 @@
         <v>138</v>
       </c>
       <c r="B139" t="str">
-        <v>Axis Bank Limited</v>
+        <v>Uno Minda Ltd</v>
       </c>
       <c r="C139" t="str">
-        <v>AXISBANK</v>
+        <v>UNOMINDA</v>
       </c>
       <c r="D139" s="1">
-        <v>1253</v>
+        <v>1112.5</v>
       </c>
       <c r="E139" s="2">
-        <v>-0.48</v>
+        <v>0.73</v>
       </c>
       <c r="F139" s="2">
-        <v>-0.48</v>
+        <v>0.41</v>
       </c>
       <c r="G139" s="2">
-        <v>2.2</v>
+        <v>-4.91</v>
       </c>
       <c r="H139" s="2">
-        <v>-1.29</v>
+        <v>-13.48</v>
       </c>
       <c r="I139" s="1">
-        <v>5684910</v>
+        <v>474105</v>
       </c>
       <c r="J139" t="str">
         <v/>
@@ -4856,28 +4856,28 @@
         <v>139</v>
       </c>
       <c r="B140" t="str">
-        <v>Marico Limited</v>
+        <v>Alkem Laboratories Limited</v>
       </c>
       <c r="C140" t="str">
-        <v>MARICO</v>
+        <v>ALKEM</v>
       </c>
       <c r="D140" s="1">
-        <v>782.4</v>
+        <v>5241.5</v>
       </c>
       <c r="E140" s="2">
-        <v>-0.48</v>
+        <v>0.7</v>
       </c>
       <c r="F140" s="2">
-        <v>-0.48</v>
+        <v>-0.71</v>
       </c>
       <c r="G140" s="2">
-        <v>-0.46</v>
+        <v>1.51</v>
       </c>
       <c r="H140" s="2">
-        <v>4.24</v>
+        <v>-4.81</v>
       </c>
       <c r="I140" s="1">
-        <v>1039988</v>
+        <v>101179</v>
       </c>
       <c r="J140" t="str">
         <v/>
@@ -4888,28 +4888,28 @@
         <v>140</v>
       </c>
       <c r="B141" t="str">
-        <v>AU Small Finance Bank Ltd</v>
+        <v>Pidilite Industries Limited</v>
       </c>
       <c r="C141" t="str">
-        <v>AUBANK</v>
+        <v>PIDILITIND</v>
       </c>
       <c r="D141" s="1">
-        <v>977.2</v>
+        <v>1488</v>
       </c>
       <c r="E141" s="2">
-        <v>-0.49</v>
+        <v>0.7</v>
       </c>
       <c r="F141" s="2">
-        <v>-0.49</v>
+        <v>0.4</v>
       </c>
       <c r="G141" s="2">
-        <v>-3.28</v>
+        <v>1.56</v>
       </c>
       <c r="H141" s="2">
-        <v>-1.74</v>
+        <v>0.38</v>
       </c>
       <c r="I141" s="1">
-        <v>1073816</v>
+        <v>509199</v>
       </c>
       <c r="J141" t="str">
         <v/>
@@ -4920,28 +4920,28 @@
         <v>141</v>
       </c>
       <c r="B142" t="str">
-        <v>The Federal Bank  Limited</v>
+        <v>Kalyan Jewellers India Ltd</v>
       </c>
       <c r="C142" t="str">
-        <v>FEDERALBNK</v>
+        <v>KALYANKJIL</v>
       </c>
       <c r="D142" s="1">
-        <v>328.2</v>
+        <v>571</v>
       </c>
       <c r="E142" s="2">
-        <v>-0.55</v>
+        <v>0.68</v>
       </c>
       <c r="F142" s="2">
-        <v>-0.55</v>
+        <v>3.07</v>
       </c>
       <c r="G142" s="2">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="H142" s="2">
-        <v>22.88</v>
+        <v>17.65</v>
       </c>
       <c r="I142" s="1">
-        <v>5094276</v>
+        <v>3630832</v>
       </c>
       <c r="J142" t="str">
         <v/>
@@ -4952,28 +4952,28 @@
         <v>142</v>
       </c>
       <c r="B143" t="str">
-        <v>Jio Financial Services Ltd</v>
+        <v>Blue Star Limited</v>
       </c>
       <c r="C143" t="str">
-        <v>JIOFIN</v>
+        <v>BLUESTARCO</v>
       </c>
       <c r="D143" s="1">
-        <v>213.45</v>
+        <v>1580</v>
       </c>
       <c r="E143" s="2">
-        <v>-0.55</v>
+        <v>0.64</v>
       </c>
       <c r="F143" s="2">
-        <v>-0.55</v>
+        <v>0.38</v>
       </c>
       <c r="G143" s="2">
-        <v>-1.58</v>
+        <v>4.08</v>
       </c>
       <c r="H143" s="2">
-        <v>-27.63</v>
+        <v>-8.71</v>
       </c>
       <c r="I143" s="1">
-        <v>7646522</v>
+        <v>233248</v>
       </c>
       <c r="J143" t="str">
         <v/>
@@ -4984,28 +4984,28 @@
         <v>143</v>
       </c>
       <c r="B144" t="str">
-        <v>Ashok Leyland Limited</v>
+        <v>Britannia Industries Limited</v>
       </c>
       <c r="C144" t="str">
-        <v>ASHOKLEY</v>
+        <v>BRITANNIA</v>
       </c>
       <c r="D144" s="1">
-        <v>144.25</v>
+        <v>4804</v>
       </c>
       <c r="E144" s="2">
-        <v>-0.56</v>
+        <v>0.62</v>
       </c>
       <c r="F144" s="2">
-        <v>-0.56</v>
+        <v>-0.44</v>
       </c>
       <c r="G144" s="2">
-        <v>-6.45</v>
+        <v>-0.54</v>
       </c>
       <c r="H144" s="2">
-        <v>-19.5</v>
+        <v>-20.34</v>
       </c>
       <c r="I144" s="1">
-        <v>12509977</v>
+        <v>59986</v>
       </c>
       <c r="J144" t="str">
         <v/>
@@ -5016,28 +5016,28 @@
         <v>144</v>
       </c>
       <c r="B145" t="str">
-        <v>Oil &amp; Natural Gas Corporation Limited</v>
+        <v>Dixon Technologies Ltd</v>
       </c>
       <c r="C145" t="str">
-        <v>ONGC</v>
+        <v>DIXON</v>
       </c>
       <c r="D145" s="1">
-        <v>220</v>
+        <v>12737</v>
       </c>
       <c r="E145" s="2">
-        <v>-0.57</v>
+        <v>0.61</v>
       </c>
       <c r="F145" s="2">
-        <v>-0.57</v>
+        <v>-0.29</v>
       </c>
       <c r="G145" s="2">
-        <v>-2.57</v>
+        <v>-2.77</v>
       </c>
       <c r="H145" s="2">
-        <v>-8.48</v>
+        <v>5.25</v>
       </c>
       <c r="I145" s="1">
-        <v>9218768</v>
+        <v>130983</v>
       </c>
       <c r="J145" t="str">
         <v/>
@@ -5048,28 +5048,28 @@
         <v>145</v>
       </c>
       <c r="B146" t="str">
-        <v>The Indian Hotels Company Limited</v>
+        <v>Adani Green Energy Ltd</v>
       </c>
       <c r="C146" t="str">
-        <v>INDHOTEL</v>
+        <v>ADANIGREEN</v>
       </c>
       <c r="D146" s="1">
-        <v>711.5</v>
+        <v>1281.4</v>
       </c>
       <c r="E146" s="2">
-        <v>-0.58</v>
+        <v>0.58</v>
       </c>
       <c r="F146" s="2">
-        <v>-0.58</v>
+        <v>2.04</v>
       </c>
       <c r="G146" s="2">
-        <v>-2.35</v>
+        <v>0.27</v>
       </c>
       <c r="H146" s="2">
-        <v>-3.7</v>
+        <v>26.23</v>
       </c>
       <c r="I146" s="1">
-        <v>2159163</v>
+        <v>1489438</v>
       </c>
       <c r="J146" t="str">
         <v/>
@@ -5080,28 +5080,28 @@
         <v>146</v>
       </c>
       <c r="B147" t="str">
-        <v>SBI Cards &amp; Payment Services Ltd</v>
+        <v>Indian Oil Corporation Limited</v>
       </c>
       <c r="C147" t="str">
-        <v>SBICARD</v>
+        <v>IOC</v>
       </c>
       <c r="D147" s="1">
-        <v>558.7</v>
+        <v>126.05</v>
       </c>
       <c r="E147" s="2">
-        <v>-0.59</v>
+        <v>0.56</v>
       </c>
       <c r="F147" s="2">
-        <v>-0.59</v>
+        <v>-0.24</v>
       </c>
       <c r="G147" s="2">
-        <v>-3.35</v>
+        <v>-6.58</v>
       </c>
       <c r="H147" s="2">
-        <v>-35.16</v>
+        <v>-24.28</v>
       </c>
       <c r="I147" s="1">
-        <v>373734</v>
+        <v>5609911</v>
       </c>
       <c r="J147" t="str">
         <v/>
@@ -5112,28 +5112,28 @@
         <v>147</v>
       </c>
       <c r="B148" t="str">
-        <v>BANKNIFTY</v>
+        <v>TATA Consumer Products Ltd</v>
       </c>
       <c r="C148" t="str">
-        <v>BANKNIFTY</v>
+        <v>TATACONSUM</v>
       </c>
       <c r="D148" s="1">
-        <v>54918</v>
+        <v>963.95</v>
       </c>
       <c r="E148" s="2">
-        <v>-0.61</v>
+        <v>0.54</v>
       </c>
       <c r="F148" s="2">
-        <v>-0.61</v>
+        <v>0.94</v>
       </c>
       <c r="G148" s="2">
-        <v>0.52</v>
+        <v>1.52</v>
       </c>
       <c r="H148" s="2">
-        <v>-7.83</v>
+        <v>-19.13</v>
       </c>
       <c r="I148" s="1">
-        <v>0</v>
+        <v>1758438</v>
       </c>
       <c r="J148" t="str">
         <v/>
@@ -5144,28 +5144,28 @@
         <v>148</v>
       </c>
       <c r="B149" t="str">
-        <v>Nestle India Limited</v>
+        <v>Tata Motors Passenger Vehicles Ltd</v>
       </c>
       <c r="C149" t="str">
-        <v>NESTLEIND</v>
+        <v>TMPV</v>
       </c>
       <c r="D149" s="1">
-        <v>1324.7</v>
+        <v>286</v>
       </c>
       <c r="E149" s="2">
-        <v>-0.62</v>
+        <v>0.54</v>
       </c>
       <c r="F149" s="2">
-        <v>-0.62</v>
+        <v>2.18</v>
       </c>
       <c r="G149" s="2">
-        <v>1.12</v>
+        <v>0.88</v>
       </c>
       <c r="H149" s="2">
-        <v>2.85</v>
+        <v>-22.15</v>
       </c>
       <c r="I149" s="1">
-        <v>1351575</v>
+        <v>9102122</v>
       </c>
       <c r="J149" t="str">
         <v/>
@@ -5176,28 +5176,28 @@
         <v>149</v>
       </c>
       <c r="B150" t="str">
-        <v>Ntpc Limited</v>
+        <v>Eicher Motors Limited</v>
       </c>
       <c r="C150" t="str">
-        <v>NTPC</v>
+        <v>EICHERMOT</v>
       </c>
       <c r="D150" s="1">
-        <v>310</v>
+        <v>7156</v>
       </c>
       <c r="E150" s="2">
-        <v>-0.64</v>
+        <v>0.52</v>
       </c>
       <c r="F150" s="2">
-        <v>-0.64</v>
+        <v>1.5</v>
       </c>
       <c r="G150" s="2">
-        <v>-3.95</v>
+        <v>0.08</v>
       </c>
       <c r="H150" s="2">
-        <v>-5.93</v>
+        <v>-2.14</v>
       </c>
       <c r="I150" s="1">
-        <v>12834279</v>
+        <v>336506</v>
       </c>
       <c r="J150" t="str">
         <v/>
@@ -5208,28 +5208,28 @@
         <v>150</v>
       </c>
       <c r="B151" t="str">
-        <v>Bajaj Holdings &amp; Investment Limited</v>
+        <v>Godrej Consumer Products Limited</v>
       </c>
       <c r="C151" t="str">
-        <v>BAJAJHLDNG</v>
+        <v>GODREJCP</v>
       </c>
       <c r="D151" s="1">
-        <v>10750</v>
+        <v>856.45</v>
       </c>
       <c r="E151" s="2">
-        <v>-0.65</v>
+        <v>0.52</v>
       </c>
       <c r="F151" s="2">
-        <v>-0.65</v>
+        <v>-0.47</v>
       </c>
       <c r="G151" s="2">
-        <v>-0.35</v>
+        <v>0.76</v>
       </c>
       <c r="H151" s="2">
-        <v>-5.1</v>
+        <v>-29.93</v>
       </c>
       <c r="I151" s="1">
-        <v>25285</v>
+        <v>876252</v>
       </c>
       <c r="J151" t="str">
         <v/>
@@ -5240,28 +5240,28 @@
         <v>151</v>
       </c>
       <c r="B152" t="str">
-        <v>NIFTY</v>
+        <v>Nhpc Limited</v>
       </c>
       <c r="C152" t="str">
-        <v>NIFTY</v>
+        <v>NHPC</v>
       </c>
       <c r="D152" s="1">
-        <v>22363.35</v>
+        <v>73.78</v>
       </c>
       <c r="E152" s="2">
-        <v>-0.7</v>
+        <v>0.52</v>
       </c>
       <c r="F152" s="2">
-        <v>-0.7</v>
+        <v>1.08</v>
       </c>
       <c r="G152" s="2">
-        <v>-1.14</v>
+        <v>1.33</v>
       </c>
       <c r="H152" s="2">
-        <v>-14.41</v>
+        <v>-6.87</v>
       </c>
       <c r="I152" s="1">
-        <v>0</v>
+        <v>3216819</v>
       </c>
       <c r="J152" t="str">
         <v/>
@@ -5272,28 +5272,28 @@
         <v>152</v>
       </c>
       <c r="B153" t="str">
-        <v>Life Insurance Corporation of India Ltd</v>
+        <v>Sun Pharmaceuticals Industries Limited</v>
       </c>
       <c r="C153" t="str">
-        <v>LICI</v>
+        <v>SUNPHARMA</v>
       </c>
       <c r="D153" s="1">
-        <v>391.5</v>
+        <v>1768.4</v>
       </c>
       <c r="E153" s="2">
-        <v>-0.7</v>
+        <v>0.48</v>
       </c>
       <c r="F153" s="2">
-        <v>-0.7</v>
+        <v>0.48</v>
       </c>
       <c r="G153" s="2">
-        <v>-0.94</v>
+        <v>-2.65</v>
       </c>
       <c r="H153" s="2">
-        <v>-8.41</v>
+        <v>2.83</v>
       </c>
       <c r="I153" s="1">
-        <v>3574282</v>
+        <v>1091397</v>
       </c>
       <c r="J153" t="str">
         <v/>
@@ -5304,28 +5304,28 @@
         <v>153</v>
       </c>
       <c r="B154" t="str">
-        <v>Interglobe Aviation Limited</v>
+        <v>Oil India Limited</v>
       </c>
       <c r="C154" t="str">
-        <v>INDIGO</v>
+        <v>OIL</v>
       </c>
       <c r="D154" s="1">
-        <v>4795</v>
+        <v>443.5</v>
       </c>
       <c r="E154" s="2">
-        <v>-0.79</v>
+        <v>0.44</v>
       </c>
       <c r="F154" s="2">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="G154" s="2">
-        <v>-3.79</v>
+        <v>-1.15</v>
       </c>
       <c r="H154" s="2">
-        <v>-5.23</v>
+        <v>4.51</v>
       </c>
       <c r="I154" s="1">
-        <v>774970</v>
+        <v>1110937</v>
       </c>
       <c r="J154" t="str">
         <v/>
@@ -5336,28 +5336,28 @@
         <v>154</v>
       </c>
       <c r="B155" t="str">
-        <v>Bank Of India Ltd</v>
+        <v>Ntpc Limited</v>
       </c>
       <c r="C155" t="str">
-        <v>BANKINDIA</v>
+        <v>NTPC</v>
       </c>
       <c r="D155" s="1">
-        <v>133.4</v>
+        <v>311.3</v>
       </c>
       <c r="E155" s="2">
-        <v>-0.79</v>
+        <v>0.42</v>
       </c>
       <c r="F155" s="2">
-        <v>-0.79</v>
+        <v>-0.22</v>
       </c>
       <c r="G155" s="2">
-        <v>2.43</v>
+        <v>-3.55</v>
       </c>
       <c r="H155" s="2">
-        <v>-7.26</v>
+        <v>-5.54</v>
       </c>
       <c r="I155" s="1">
-        <v>6324408</v>
+        <v>5829675</v>
       </c>
       <c r="J155" t="str">
         <v/>
@@ -5368,28 +5368,28 @@
         <v>155</v>
       </c>
       <c r="B156" t="str">
-        <v>Indian Oil Corporation Limited</v>
+        <v>Ambuja Cements Limited</v>
       </c>
       <c r="C156" t="str">
-        <v>IOC</v>
+        <v>AMBUJACEM</v>
       </c>
       <c r="D156" s="1">
-        <v>125.35</v>
+        <v>349.35</v>
       </c>
       <c r="E156" s="2">
-        <v>-0.79</v>
+        <v>0.39</v>
       </c>
       <c r="F156" s="2">
-        <v>-0.79</v>
+        <v>-0.61</v>
       </c>
       <c r="G156" s="2">
-        <v>-7.1</v>
+        <v>-6.59</v>
       </c>
       <c r="H156" s="2">
-        <v>-24.7</v>
+        <v>-37.21</v>
       </c>
       <c r="I156" s="1">
-        <v>10605346</v>
+        <v>2452516</v>
       </c>
       <c r="J156" t="str">
         <v/>
@@ -5400,28 +5400,28 @@
         <v>156</v>
       </c>
       <c r="B157" t="str">
-        <v>Punjab National Bank Ltd</v>
+        <v>Motilal Oswal Financial Services Limited</v>
       </c>
       <c r="C157" t="str">
-        <v>PNB</v>
+        <v>MOTILALOFS</v>
       </c>
       <c r="D157" s="1">
-        <v>116</v>
+        <v>1055</v>
       </c>
       <c r="E157" s="2">
-        <v>-0.84</v>
+        <v>0.38</v>
       </c>
       <c r="F157" s="2">
-        <v>-0.84</v>
+        <v>2.83</v>
       </c>
       <c r="G157" s="2">
-        <v>2.6</v>
+        <v>6.14</v>
       </c>
       <c r="H157" s="2">
-        <v>-6.13</v>
+        <v>23.28</v>
       </c>
       <c r="I157" s="1">
-        <v>8980416</v>
+        <v>562673</v>
       </c>
       <c r="J157" t="str">
         <v/>
@@ -5432,28 +5432,28 @@
         <v>157</v>
       </c>
       <c r="B158" t="str">
-        <v>Bajaj Finserv Limited</v>
+        <v>Indus Towers Ltd (Bharti Infratel)</v>
       </c>
       <c r="C158" t="str">
-        <v>BAJAJFINSV</v>
+        <v>INDUSTOWER</v>
       </c>
       <c r="D158" s="1">
-        <v>1719.9</v>
+        <v>376.95</v>
       </c>
       <c r="E158" s="2">
-        <v>-0.85</v>
+        <v>0.35</v>
       </c>
       <c r="F158" s="2">
-        <v>-0.85</v>
+        <v>-1.02</v>
       </c>
       <c r="G158" s="2">
-        <v>-0.64</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2">
-        <v>-15.69</v>
+        <v>-9.98</v>
       </c>
       <c r="I158" s="1">
-        <v>565062</v>
+        <v>1683358</v>
       </c>
       <c r="J158" t="str">
         <v/>
@@ -5464,28 +5464,28 @@
         <v>158</v>
       </c>
       <c r="B159" t="str">
-        <v>Biocon Limited</v>
+        <v>Adani Ports And Special Economic Zone Limited</v>
       </c>
       <c r="C159" t="str">
-        <v>BIOCON</v>
+        <v>ADANIPORTS</v>
       </c>
       <c r="D159" s="1">
-        <v>346.35</v>
+        <v>1759.5</v>
       </c>
       <c r="E159" s="2">
-        <v>-0.87</v>
+        <v>0.31</v>
       </c>
       <c r="F159" s="2">
-        <v>-0.87</v>
+        <v>-0.09</v>
       </c>
       <c r="G159" s="2">
-        <v>-6.47</v>
+        <v>-2.16</v>
       </c>
       <c r="H159" s="2">
-        <v>-12.07</v>
+        <v>19.71</v>
       </c>
       <c r="I159" s="1">
-        <v>2632161</v>
+        <v>3406736</v>
       </c>
       <c r="J159" t="str">
         <v/>
@@ -5496,28 +5496,28 @@
         <v>159</v>
       </c>
       <c r="B160" t="str">
-        <v>FSN E-Commerce Ventures Ltd</v>
+        <v>Supreme Industries Limited</v>
       </c>
       <c r="C160" t="str">
-        <v>NYKAA</v>
+        <v>SUPREMEIND</v>
       </c>
       <c r="D160" s="1">
-        <v>340</v>
+        <v>3504</v>
       </c>
       <c r="E160" s="2">
-        <v>-0.87</v>
+        <v>0.29</v>
       </c>
       <c r="F160" s="2">
-        <v>-0.87</v>
+        <v>0.84</v>
       </c>
       <c r="G160" s="2">
-        <v>6.25</v>
+        <v>1.54</v>
       </c>
       <c r="H160" s="2">
-        <v>28.23</v>
+        <v>4.48</v>
       </c>
       <c r="I160" s="1">
-        <v>2223568</v>
+        <v>76458</v>
       </c>
       <c r="J160" t="str">
         <v/>
@@ -5528,28 +5528,28 @@
         <v>160</v>
       </c>
       <c r="B161" t="str">
-        <v>Dixon Technologies Ltd</v>
+        <v>Page Industries Limited</v>
       </c>
       <c r="C161" t="str">
-        <v>DIXON</v>
+        <v>PAGEIND</v>
       </c>
       <c r="D161" s="1">
-        <v>12660</v>
+        <v>37000</v>
       </c>
       <c r="E161" s="2">
-        <v>-0.89</v>
+        <v>0.26</v>
       </c>
       <c r="F161" s="2">
-        <v>-0.89</v>
+        <v>0.34</v>
       </c>
       <c r="G161" s="2">
-        <v>-3.36</v>
+        <v>1.69</v>
       </c>
       <c r="H161" s="2">
-        <v>4.61</v>
+        <v>2.65</v>
       </c>
       <c r="I161" s="1">
-        <v>172532</v>
+        <v>13953</v>
       </c>
       <c r="J161" t="str">
         <v/>
@@ -5560,28 +5560,28 @@
         <v>161</v>
       </c>
       <c r="B162" t="str">
-        <v>Tata Steel Limited</v>
+        <v>SBI Life Insurance Company Ltd</v>
       </c>
       <c r="C162" t="str">
-        <v>TATASTEEL</v>
+        <v>SBILIFE</v>
       </c>
       <c r="D162" s="1">
-        <v>172.24</v>
+        <v>1684.5</v>
       </c>
       <c r="E162" s="2">
-        <v>-0.9</v>
+        <v>0.22</v>
       </c>
       <c r="F162" s="2">
-        <v>-0.9</v>
+        <v>-0.01</v>
       </c>
       <c r="G162" s="2">
-        <v>-6.54</v>
+        <v>-0.7</v>
       </c>
       <c r="H162" s="2">
-        <v>-4.35</v>
+        <v>-17.22</v>
       </c>
       <c r="I162" s="1">
-        <v>27079930</v>
+        <v>1579893</v>
       </c>
       <c r="J162" t="str">
         <v/>
@@ -5592,28 +5592,28 @@
         <v>162</v>
       </c>
       <c r="B163" t="str">
-        <v>Maruti Suzuki India Limited</v>
+        <v>Bank Of India Ltd</v>
       </c>
       <c r="C163" t="str">
-        <v>MARUTI</v>
+        <v>BANKINDIA</v>
       </c>
       <c r="D163" s="1">
-        <v>11315</v>
+        <v>133.7</v>
       </c>
       <c r="E163" s="2">
-        <v>-0.92</v>
+        <v>0.22</v>
       </c>
       <c r="F163" s="2">
-        <v>-0.92</v>
+        <v>-0.57</v>
       </c>
       <c r="G163" s="2">
-        <v>-5.45</v>
+        <v>2.66</v>
       </c>
       <c r="H163" s="2">
-        <v>-32.23</v>
+        <v>-7.06</v>
       </c>
       <c r="I163" s="1">
-        <v>323997</v>
+        <v>7433846</v>
       </c>
       <c r="J163" t="str">
         <v/>
@@ -5624,28 +5624,28 @@
         <v>163</v>
       </c>
       <c r="B164" t="str">
-        <v>ICICI Lombard General Insurance Company Ltd</v>
+        <v>Jsw Steel Limited</v>
       </c>
       <c r="C164" t="str">
-        <v>ICICIGI</v>
+        <v>JSWSTEEL</v>
       </c>
       <c r="D164" s="1">
-        <v>1674</v>
+        <v>1175</v>
       </c>
       <c r="E164" s="2">
-        <v>-0.96</v>
+        <v>0.17</v>
       </c>
       <c r="F164" s="2">
-        <v>-0.96</v>
+        <v>0.6</v>
       </c>
       <c r="G164" s="2">
-        <v>5.28</v>
+        <v>-6.26</v>
       </c>
       <c r="H164" s="2">
-        <v>-14.68</v>
+        <v>0.88</v>
       </c>
       <c r="I164" s="1">
-        <v>748749</v>
+        <v>741618</v>
       </c>
       <c r="J164" t="str">
         <v/>
@@ -5656,28 +5656,28 @@
         <v>164</v>
       </c>
       <c r="B165" t="str">
-        <v>Reliance Industries Limited</v>
+        <v>Pi Industries Limited</v>
       </c>
       <c r="C165" t="str">
-        <v>RELIANCE</v>
+        <v>PIIND</v>
       </c>
       <c r="D165" s="1">
-        <v>1158.9</v>
+        <v>2135</v>
       </c>
       <c r="E165" s="2">
-        <v>-0.97</v>
+        <v>0.16</v>
       </c>
       <c r="F165" s="2">
-        <v>-0.97</v>
+        <v>0.79</v>
       </c>
       <c r="G165" s="2">
-        <v>-2.37</v>
+        <v>-7.58</v>
       </c>
       <c r="H165" s="2">
-        <v>-26.2</v>
+        <v>-34.07</v>
       </c>
       <c r="I165" s="1">
-        <v>11338332</v>
+        <v>335199</v>
       </c>
       <c r="J165" t="str">
         <v/>
@@ -5688,28 +5688,28 @@
         <v>165</v>
       </c>
       <c r="B166" t="str">
-        <v>Godrej Consumer Products Limited</v>
+        <v>Tata Power Company Limited</v>
       </c>
       <c r="C166" t="str">
-        <v>GODREJCP</v>
+        <v>TATAPOWER</v>
       </c>
       <c r="D166" s="1">
-        <v>852.05</v>
+        <v>344.2</v>
       </c>
       <c r="E166" s="2">
-        <v>-0.98</v>
+        <v>0.15</v>
       </c>
       <c r="F166" s="2">
-        <v>-0.98</v>
+        <v>0.6</v>
       </c>
       <c r="G166" s="2">
-        <v>0.24</v>
+        <v>-4.12</v>
       </c>
       <c r="H166" s="2">
-        <v>-30.29</v>
+        <v>-9.33</v>
       </c>
       <c r="I166" s="1">
-        <v>339250</v>
+        <v>2311528</v>
       </c>
       <c r="J166" t="str">
         <v/>
@@ -5720,28 +5720,28 @@
         <v>166</v>
       </c>
       <c r="B167" t="str">
-        <v>Shree Cements Limited</v>
+        <v>Bharat Heavy Electricals Limited</v>
       </c>
       <c r="C167" t="str">
-        <v>SHREECEM</v>
+        <v>BHEL</v>
       </c>
       <c r="D167" s="1">
-        <v>21860</v>
+        <v>440.35</v>
       </c>
       <c r="E167" s="2">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="F167" s="2">
-        <v>-1</v>
+        <v>1.56</v>
       </c>
       <c r="G167" s="2">
-        <v>-2.17</v>
+        <v>5.98</v>
       </c>
       <c r="H167" s="2">
-        <v>-17.74</v>
+        <v>53.19</v>
       </c>
       <c r="I167" s="1">
-        <v>36998</v>
+        <v>15750496</v>
       </c>
       <c r="J167" t="str">
         <v/>
@@ -5752,28 +5752,28 @@
         <v>167</v>
       </c>
       <c r="B168" t="str">
-        <v>Indusind Bank Limited</v>
+        <v>Interglobe Aviation Limited</v>
       </c>
       <c r="C168" t="str">
-        <v>INDUSINDBK</v>
+        <v>INDIGO</v>
       </c>
       <c r="D168" s="1">
-        <v>853</v>
+        <v>4799.2</v>
       </c>
       <c r="E168" s="2">
-        <v>-1</v>
+        <v>0.09</v>
       </c>
       <c r="F168" s="2">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="G168" s="2">
-        <v>-5.37</v>
+        <v>-3.71</v>
       </c>
       <c r="H168" s="2">
-        <v>-1.3</v>
+        <v>-5.14</v>
       </c>
       <c r="I168" s="1">
-        <v>5115608</v>
+        <v>392510</v>
       </c>
       <c r="J168" t="str">
         <v/>
@@ -5784,28 +5784,28 @@
         <v>168</v>
       </c>
       <c r="B169" t="str">
-        <v>Ambuja Cements Limited</v>
+        <v>Union Bank Of India Ltd</v>
       </c>
       <c r="C169" t="str">
-        <v>AMBUJACEM</v>
+        <v>UNIONBANK</v>
       </c>
       <c r="D169" s="1">
-        <v>348</v>
+        <v>171.41</v>
       </c>
       <c r="E169" s="2">
-        <v>-1</v>
+        <v>0.05</v>
       </c>
       <c r="F169" s="2">
-        <v>-1</v>
+        <v>-0.95</v>
       </c>
       <c r="G169" s="2">
-        <v>-6.95</v>
+        <v>0.24</v>
       </c>
       <c r="H169" s="2">
-        <v>-37.45</v>
+        <v>11.48</v>
       </c>
       <c r="I169" s="1">
-        <v>2236843</v>
+        <v>11482032</v>
       </c>
       <c r="J169" t="str">
         <v/>
@@ -5816,28 +5816,28 @@
         <v>169</v>
       </c>
       <c r="B170" t="str">
-        <v>Union Bank Of India Ltd</v>
+        <v>Radico Khaitan Limited</v>
       </c>
       <c r="C170" t="str">
-        <v>UNIONBANK</v>
+        <v>RADICO</v>
       </c>
       <c r="D170" s="1">
-        <v>171.33</v>
+        <v>4557</v>
       </c>
       <c r="E170" s="2">
-        <v>-1</v>
+        <v>0.04</v>
       </c>
       <c r="F170" s="2">
-        <v>-1</v>
+        <v>0.15</v>
       </c>
       <c r="G170" s="2">
-        <v>0.19</v>
+        <v>4.37</v>
       </c>
       <c r="H170" s="2">
-        <v>11.43</v>
+        <v>38.16</v>
       </c>
       <c r="I170" s="1">
-        <v>4401142</v>
+        <v>97597</v>
       </c>
       <c r="J170" t="str">
         <v/>
@@ -5848,28 +5848,28 @@
         <v>170</v>
       </c>
       <c r="B171" t="str">
-        <v>Canara Bank Ltd</v>
+        <v>Avenue Supermarts Ltd</v>
       </c>
       <c r="C171" t="str">
-        <v>CANBK</v>
+        <v>DMART</v>
       </c>
       <c r="D171" s="1">
-        <v>118.38</v>
+        <v>3366</v>
       </c>
       <c r="E171" s="2">
-        <v>-1.01</v>
+        <v>0.03</v>
       </c>
       <c r="F171" s="2">
-        <v>-1.01</v>
+        <v>-4.29</v>
       </c>
       <c r="G171" s="2">
-        <v>-0.89</v>
+        <v>-11.45</v>
       </c>
       <c r="H171" s="2">
-        <v>-23.58</v>
+        <v>-11</v>
       </c>
       <c r="I171" s="1">
-        <v>9100287</v>
+        <v>421647</v>
       </c>
       <c r="J171" t="str">
         <v/>
@@ -5880,28 +5880,28 @@
         <v>171</v>
       </c>
       <c r="B172" t="str">
-        <v>Britannia Industries Limited</v>
+        <v>Adani Power Limited</v>
       </c>
       <c r="C172" t="str">
-        <v>BRITANNIA</v>
+        <v>ADANIPOWER</v>
       </c>
       <c r="D172" s="1">
-        <v>4774.5</v>
+        <v>185.95</v>
       </c>
       <c r="E172" s="2">
-        <v>-1.05</v>
+        <v>0.03</v>
       </c>
       <c r="F172" s="2">
-        <v>-1.05</v>
+        <v>-1.61</v>
       </c>
       <c r="G172" s="2">
-        <v>-1.15</v>
+        <v>-8.85</v>
       </c>
       <c r="H172" s="2">
-        <v>-20.83</v>
+        <v>30.04</v>
       </c>
       <c r="I172" s="1">
-        <v>65623</v>
+        <v>14731249</v>
       </c>
       <c r="J172" t="str">
         <v/>
@@ -5912,28 +5912,28 @@
         <v>172</v>
       </c>
       <c r="B173" t="str">
-        <v>Lupin Limited</v>
+        <v>Siemens Energy India Ltd</v>
       </c>
       <c r="C173" t="str">
-        <v>LUPIN</v>
+        <v>ENRIN</v>
       </c>
       <c r="D173" s="1">
-        <v>1935</v>
+        <v>3116.5</v>
       </c>
       <c r="E173" s="2">
-        <v>-1.1</v>
+        <v>-0.05</v>
       </c>
       <c r="F173" s="2">
-        <v>-1.1</v>
+        <v>0.5</v>
       </c>
       <c r="G173" s="2">
-        <v>-4.69</v>
+        <v>-2.61</v>
       </c>
       <c r="H173" s="2">
-        <v>-8.27</v>
+        <v>21.73</v>
       </c>
       <c r="I173" s="1">
-        <v>418279</v>
+        <v>309073</v>
       </c>
       <c r="J173" t="str">
         <v/>
@@ -5944,28 +5944,28 @@
         <v>173</v>
       </c>
       <c r="B174" t="str">
-        <v>Grasim Industries Limited</v>
+        <v>Hindustan Zinc Limited</v>
       </c>
       <c r="C174" t="str">
-        <v>GRASIM</v>
+        <v>HINDZINC</v>
       </c>
       <c r="D174" s="1">
-        <v>2858</v>
+        <v>546.6</v>
       </c>
       <c r="E174" s="2">
-        <v>-1.11</v>
+        <v>-0.05</v>
       </c>
       <c r="F174" s="2">
-        <v>-1.11</v>
+        <v>0.57</v>
       </c>
       <c r="G174" s="2">
-        <v>-6.66</v>
+        <v>-3.43</v>
       </c>
       <c r="H174" s="2">
-        <v>1.03</v>
+        <v>-10.75</v>
       </c>
       <c r="I174" s="1">
-        <v>117363</v>
+        <v>1351965</v>
       </c>
       <c r="J174" t="str">
         <v/>
@@ -5976,28 +5976,28 @@
         <v>174</v>
       </c>
       <c r="B175" t="str">
-        <v>Icici Bank Limited</v>
+        <v>Bajaj Holdings &amp; Investment Limited</v>
       </c>
       <c r="C175" t="str">
-        <v>ICICIBANK</v>
+        <v>BAJAJHLDNG</v>
       </c>
       <c r="D175" s="1">
-        <v>1340</v>
+        <v>10740</v>
       </c>
       <c r="E175" s="2">
-        <v>-1.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F175" s="2">
-        <v>-1.11</v>
+        <v>-0.74</v>
       </c>
       <c r="G175" s="2">
-        <v>1.38</v>
+        <v>-0.44</v>
       </c>
       <c r="H175" s="2">
-        <v>-0.22</v>
+        <v>-5.19</v>
       </c>
       <c r="I175" s="1">
-        <v>8605258</v>
+        <v>24987</v>
       </c>
       <c r="J175" t="str">
         <v/>
@@ -6008,28 +6008,28 @@
         <v>175</v>
       </c>
       <c r="B176" t="str">
-        <v>Coforge (Niit Tech) Ltd</v>
+        <v>HDFC Life Insurance Company Ltd</v>
       </c>
       <c r="C176" t="str">
-        <v>COFORGE</v>
+        <v>HDFCLIFE</v>
       </c>
       <c r="D176" s="1">
-        <v>1846.6</v>
+        <v>558.45</v>
       </c>
       <c r="E176" s="2">
-        <v>-1.14</v>
+        <v>-0.14</v>
       </c>
       <c r="F176" s="2">
-        <v>-1.14</v>
+        <v>0.32</v>
       </c>
       <c r="G176" s="2">
-        <v>5.57</v>
+        <v>7.15</v>
       </c>
       <c r="H176" s="2">
-        <v>11.04</v>
+        <v>-25.53</v>
       </c>
       <c r="I176" s="1">
-        <v>1259800</v>
+        <v>1542673</v>
       </c>
       <c r="J176" t="str">
         <v/>
@@ -6040,28 +6040,28 @@
         <v>176</v>
       </c>
       <c r="B177" t="str">
-        <v>Bharat Petroleum Corporation Limited</v>
+        <v>The Federal Bank  Limited</v>
       </c>
       <c r="C177" t="str">
-        <v>BPCL</v>
+        <v>FEDERALBNK</v>
       </c>
       <c r="D177" s="1">
-        <v>284.5</v>
+        <v>327.75</v>
       </c>
       <c r="E177" s="2">
-        <v>-1.15</v>
+        <v>-0.14</v>
       </c>
       <c r="F177" s="2">
-        <v>-1.15</v>
+        <v>-0.68</v>
       </c>
       <c r="G177" s="2">
-        <v>-6.17</v>
+        <v>3.26</v>
       </c>
       <c r="H177" s="2">
-        <v>-25.91</v>
+        <v>22.71</v>
       </c>
       <c r="I177" s="1">
-        <v>4312619</v>
+        <v>2556830</v>
       </c>
       <c r="J177" t="str">
         <v/>
@@ -6072,28 +6072,28 @@
         <v>177</v>
       </c>
       <c r="B178" t="str">
-        <v>Godfrey Phillips India Limited</v>
+        <v>Petronet Lng Limited</v>
       </c>
       <c r="C178" t="str">
-        <v>GODFRYPHLP</v>
+        <v>PETRONET</v>
       </c>
       <c r="D178" s="1">
-        <v>1791.8</v>
+        <v>290.05</v>
       </c>
       <c r="E178" s="2">
-        <v>-1.18</v>
+        <v>-0.15</v>
       </c>
       <c r="F178" s="2">
-        <v>-1.18</v>
+        <v>-0.5</v>
       </c>
       <c r="G178" s="2">
-        <v>-5.29</v>
+        <v>1.95</v>
       </c>
       <c r="H178" s="2">
-        <v>-35.13</v>
+        <v>2.09</v>
       </c>
       <c r="I178" s="1">
-        <v>219747</v>
+        <v>1272157</v>
       </c>
       <c r="J178" t="str">
         <v/>
@@ -6104,28 +6104,28 @@
         <v>178</v>
       </c>
       <c r="B179" t="str">
-        <v>Shriram Finance Ltd</v>
+        <v>Bank Of Maharashtra Ltd</v>
       </c>
       <c r="C179" t="str">
-        <v>SHRIRAMFIN</v>
+        <v>MAHABANK</v>
       </c>
       <c r="D179" s="1">
-        <v>929.4</v>
+        <v>82.85</v>
       </c>
       <c r="E179" s="2">
-        <v>-1.18</v>
+        <v>-0.18</v>
       </c>
       <c r="F179" s="2">
-        <v>-1.18</v>
+        <v>-0.37</v>
       </c>
       <c r="G179" s="2">
-        <v>-5.42</v>
+        <v>4.38</v>
       </c>
       <c r="H179" s="2">
-        <v>-6.71</v>
+        <v>33.52</v>
       </c>
       <c r="I179" s="1">
-        <v>1976078</v>
+        <v>11606741</v>
       </c>
       <c r="J179" t="str">
         <v/>
@@ -6136,28 +6136,28 @@
         <v>179</v>
       </c>
       <c r="B180" t="str">
-        <v>United Spirits Ltd</v>
+        <v>Pg Electroplast Limited</v>
       </c>
       <c r="C180" t="str">
-        <v>UNITDSPR</v>
+        <v>PGEL</v>
       </c>
       <c r="D180" s="1">
-        <v>1349.7</v>
+        <v>524</v>
       </c>
       <c r="E180" s="2">
-        <v>-1.19</v>
+        <v>-0.19</v>
       </c>
       <c r="F180" s="2">
-        <v>-1.19</v>
+        <v>2.38</v>
       </c>
       <c r="G180" s="2">
-        <v>-0.32</v>
+        <v>6.19</v>
       </c>
       <c r="H180" s="2">
-        <v>-6.51</v>
+        <v>-8.92</v>
       </c>
       <c r="I180" s="1">
-        <v>473799</v>
+        <v>576516</v>
       </c>
       <c r="J180" t="str">
         <v/>
@@ -6168,28 +6168,28 @@
         <v>180</v>
       </c>
       <c r="B181" t="str">
-        <v>Srf Limited</v>
+        <v>Power Grid Corporation Of India Limited</v>
       </c>
       <c r="C181" t="str">
-        <v>SRF</v>
+        <v>POWERGRID</v>
       </c>
       <c r="D181" s="1">
-        <v>2488.4</v>
+        <v>248.45</v>
       </c>
       <c r="E181" s="2">
-        <v>-1.23</v>
+        <v>-0.22</v>
       </c>
       <c r="F181" s="2">
-        <v>-1.23</v>
+        <v>-0.28</v>
       </c>
       <c r="G181" s="2">
-        <v>0.64</v>
+        <v>-4.63</v>
       </c>
       <c r="H181" s="2">
-        <v>-19.08</v>
+        <v>-6.1</v>
       </c>
       <c r="I181" s="1">
-        <v>156201</v>
+        <v>12158472</v>
       </c>
       <c r="J181" t="str">
         <v/>
@@ -6200,28 +6200,28 @@
         <v>181</v>
       </c>
       <c r="B182" t="str">
-        <v>Vishal Mega Mart Ltd</v>
+        <v>Premier Energies Ltd</v>
       </c>
       <c r="C182" t="str">
-        <v>VMM</v>
+        <v>PREMIERENE</v>
       </c>
       <c r="D182" s="1">
-        <v>96.3</v>
+        <v>906.7</v>
       </c>
       <c r="E182" s="2">
-        <v>-1.23</v>
+        <v>-0.24</v>
       </c>
       <c r="F182" s="2">
-        <v>-1.23</v>
+        <v>1.27</v>
       </c>
       <c r="G182" s="2">
-        <v>-4.65</v>
+        <v>4.21</v>
       </c>
       <c r="H182" s="2">
-        <v>-29.38</v>
+        <v>7.66</v>
       </c>
       <c r="I182" s="1">
-        <v>5877580</v>
+        <v>786663</v>
       </c>
       <c r="J182" t="str">
         <v/>
@@ -6232,28 +6232,28 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>Info Edge (india) Limited</v>
+        <v>Glenmark Pharmaceuticals Limited</v>
       </c>
       <c r="C183" t="str">
-        <v>NAUKRI</v>
+        <v>GLENMARK</v>
       </c>
       <c r="D183" s="1">
-        <v>1203.9</v>
+        <v>2277</v>
       </c>
       <c r="E183" s="2">
-        <v>-1.24</v>
+        <v>-0.26</v>
       </c>
       <c r="F183" s="2">
-        <v>-1.24</v>
+        <v>-0.7</v>
       </c>
       <c r="G183" s="2">
-        <v>-1.28</v>
+        <v>-2.47</v>
       </c>
       <c r="H183" s="2">
-        <v>-9.73</v>
+        <v>11.88</v>
       </c>
       <c r="I183" s="1">
-        <v>689819</v>
+        <v>254093</v>
       </c>
       <c r="J183" t="str">
         <v/>
@@ -6264,28 +6264,28 @@
         <v>183</v>
       </c>
       <c r="B184" t="str">
-        <v>LTIMindtree Ltd</v>
+        <v>Fortis Healthcare Limited</v>
       </c>
       <c r="C184" t="str">
-        <v>LTM</v>
+        <v>FORTIS</v>
       </c>
       <c r="D184" s="1">
-        <v>4018.9</v>
+        <v>755</v>
       </c>
       <c r="E184" s="2">
-        <v>-1.26</v>
+        <v>-0.3</v>
       </c>
       <c r="F184" s="2">
-        <v>-1.26</v>
+        <v>-3.97</v>
       </c>
       <c r="G184" s="2">
-        <v>-0.65</v>
+        <v>-1.95</v>
       </c>
       <c r="H184" s="2">
-        <v>-33.72</v>
+        <v>-14.59</v>
       </c>
       <c r="I184" s="1">
-        <v>240633</v>
+        <v>2079058</v>
       </c>
       <c r="J184" t="str">
         <v/>
@@ -6296,28 +6296,28 @@
         <v>184</v>
       </c>
       <c r="B185" t="str">
-        <v>Crompton Greaves Consumer Electricals Limited</v>
+        <v>Muthoot Finance Limited</v>
       </c>
       <c r="C185" t="str">
-        <v>CROMPTON</v>
+        <v>MUTHOOTFIN</v>
       </c>
       <c r="D185" s="1">
-        <v>202.5</v>
+        <v>2626</v>
       </c>
       <c r="E185" s="2">
-        <v>-1.27</v>
+        <v>-0.31</v>
       </c>
       <c r="F185" s="2">
-        <v>-1.27</v>
+        <v>0.05</v>
       </c>
       <c r="G185" s="2">
-        <v>-2.96</v>
+        <v>-4.06</v>
       </c>
       <c r="H185" s="2">
-        <v>-19.72</v>
+        <v>-31.11</v>
       </c>
       <c r="I185" s="1">
-        <v>2878166</v>
+        <v>654557</v>
       </c>
       <c r="J185" t="str">
         <v/>
@@ -6328,28 +6328,28 @@
         <v>185</v>
       </c>
       <c r="B186" t="str">
-        <v>Kaynes Technology India Ltd</v>
+        <v>Marico Limited</v>
       </c>
       <c r="C186" t="str">
-        <v>KAYNES</v>
+        <v>MARICO</v>
       </c>
       <c r="D186" s="1">
-        <v>3222.1</v>
+        <v>780</v>
       </c>
       <c r="E186" s="2">
-        <v>-1.28</v>
+        <v>-0.31</v>
       </c>
       <c r="F186" s="2">
-        <v>-1.28</v>
+        <v>-0.78</v>
       </c>
       <c r="G186" s="2">
-        <v>-7.97</v>
+        <v>-0.76</v>
       </c>
       <c r="H186" s="2">
-        <v>-19.71</v>
+        <v>3.92</v>
       </c>
       <c r="I186" s="1">
-        <v>657971</v>
+        <v>2265221</v>
       </c>
       <c r="J186" t="str">
         <v/>
@@ -6360,28 +6360,28 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>Voltas Limited</v>
+        <v>Nestle India Limited</v>
       </c>
       <c r="C187" t="str">
-        <v>VOLTAS</v>
+        <v>NESTLEIND</v>
       </c>
       <c r="D187" s="1">
-        <v>1020</v>
+        <v>1320.4</v>
       </c>
       <c r="E187" s="2">
-        <v>-1.33</v>
+        <v>-0.32</v>
       </c>
       <c r="F187" s="2">
-        <v>-1.33</v>
+        <v>-0.95</v>
       </c>
       <c r="G187" s="2">
-        <v>-4.67</v>
+        <v>0.79</v>
       </c>
       <c r="H187" s="2">
-        <v>-25.07</v>
+        <v>2.52</v>
       </c>
       <c r="I187" s="1">
-        <v>282434</v>
+        <v>3007887</v>
       </c>
       <c r="J187" t="str">
         <v/>
@@ -6392,28 +6392,28 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Indus Towers Ltd (Bharti Infratel)</v>
+        <v>Srf Limited</v>
       </c>
       <c r="C188" t="str">
-        <v>INDUSTOWER</v>
+        <v>SRF</v>
       </c>
       <c r="D188" s="1">
-        <v>375.65</v>
+        <v>2479.2</v>
       </c>
       <c r="E188" s="2">
-        <v>-1.37</v>
+        <v>-0.37</v>
       </c>
       <c r="F188" s="2">
-        <v>-1.37</v>
+        <v>-1.6</v>
       </c>
       <c r="G188" s="2">
-        <v>0.66</v>
+        <v>0.27</v>
       </c>
       <c r="H188" s="2">
-        <v>-10.29</v>
+        <v>-19.38</v>
       </c>
       <c r="I188" s="1">
-        <v>5835701</v>
+        <v>127335</v>
       </c>
       <c r="J188" t="str">
         <v/>
@@ -6424,28 +6424,28 @@
         <v>188</v>
       </c>
       <c r="B189" t="str">
-        <v>Alkem Laboratories Limited</v>
+        <v>Cummins India Limited</v>
       </c>
       <c r="C189" t="str">
-        <v>ALKEM</v>
+        <v>CUMMINSIND</v>
       </c>
       <c r="D189" s="1">
-        <v>5205</v>
+        <v>4815</v>
       </c>
       <c r="E189" s="2">
-        <v>-1.4</v>
+        <v>-0.41</v>
       </c>
       <c r="F189" s="2">
-        <v>-1.4</v>
+        <v>-0.31</v>
       </c>
       <c r="G189" s="2">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="H189" s="2">
-        <v>-5.48</v>
+        <v>8.58</v>
       </c>
       <c r="I189" s="1">
-        <v>179595</v>
+        <v>298411</v>
       </c>
       <c r="J189" t="str">
         <v/>
@@ -6456,28 +6456,28 @@
         <v>189</v>
       </c>
       <c r="B190" t="str">
-        <v>Oracle Financial Services Software Limited</v>
+        <v>Laurus Labs Limited</v>
       </c>
       <c r="C190" t="str">
-        <v>OFSS</v>
+        <v>LAURUSLABS</v>
       </c>
       <c r="D190" s="1">
-        <v>10360</v>
+        <v>2060</v>
       </c>
       <c r="E190" s="2">
-        <v>-1.43</v>
+        <v>-0.44</v>
       </c>
       <c r="F190" s="2">
-        <v>-1.43</v>
+        <v>1.15</v>
       </c>
       <c r="G190" s="2">
-        <v>-2.54</v>
+        <v>4.04</v>
       </c>
       <c r="H190" s="2">
-        <v>34.77</v>
+        <v>85.92</v>
       </c>
       <c r="I190" s="1">
-        <v>262535</v>
+        <v>1108160</v>
       </c>
       <c r="J190" t="str">
         <v/>
@@ -6488,28 +6488,28 @@
         <v>190</v>
       </c>
       <c r="B191" t="str">
-        <v>Tata Consultancy Services Limited</v>
+        <v>Max Healthcare Institute Ltd</v>
       </c>
       <c r="C191" t="str">
-        <v>TCS</v>
+        <v>MAXHEALTH</v>
       </c>
       <c r="D191" s="1">
-        <v>2125</v>
+        <v>861.85</v>
       </c>
       <c r="E191" s="2">
-        <v>-1.44</v>
+        <v>-0.47</v>
       </c>
       <c r="F191" s="2">
-        <v>-1.44</v>
+        <v>-2.48</v>
       </c>
       <c r="G191" s="2">
-        <v>3.63</v>
+        <v>-7.31</v>
       </c>
       <c r="H191" s="2">
-        <v>-33.72</v>
+        <v>-17.53</v>
       </c>
       <c r="I191" s="1">
-        <v>3540523</v>
+        <v>3957032</v>
       </c>
       <c r="J191" t="str">
         <v/>
@@ -6520,28 +6520,28 @@
         <v>191</v>
       </c>
       <c r="B192" t="str">
-        <v>Ultratech Cement Limited</v>
+        <v>Zydus Lifesciences Ltd</v>
       </c>
       <c r="C192" t="str">
-        <v>ULTRACEMCO</v>
+        <v>ZYDUSLIFE</v>
       </c>
       <c r="D192" s="1">
-        <v>10520</v>
+        <v>1129</v>
       </c>
       <c r="E192" s="2">
-        <v>-1.45</v>
+        <v>-0.48</v>
       </c>
       <c r="F192" s="2">
-        <v>-1.45</v>
+        <v>1.03</v>
       </c>
       <c r="G192" s="2">
-        <v>-3.98</v>
+        <v>-2.84</v>
       </c>
       <c r="H192" s="2">
-        <v>-10.73</v>
+        <v>23.48</v>
       </c>
       <c r="I192" s="1">
-        <v>220407</v>
+        <v>1098228</v>
       </c>
       <c r="J192" t="str">
         <v/>
@@ -6552,28 +6552,28 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>Bharti Airtel Limited</v>
+        <v>Kei Industries Limited</v>
       </c>
       <c r="C193" t="str">
-        <v>BHARTIARTL</v>
+        <v>KEI</v>
       </c>
       <c r="D193" s="1">
-        <v>1778.7</v>
+        <v>4630.2</v>
       </c>
       <c r="E193" s="2">
-        <v>-1.46</v>
+        <v>-0.52</v>
       </c>
       <c r="F193" s="2">
-        <v>-1.46</v>
+        <v>0.99</v>
       </c>
       <c r="G193" s="2">
-        <v>1.24</v>
+        <v>3.93</v>
       </c>
       <c r="H193" s="2">
-        <v>-15.53</v>
+        <v>3.81</v>
       </c>
       <c r="I193" s="1">
-        <v>4819377</v>
+        <v>332887</v>
       </c>
       <c r="J193" t="str">
         <v/>
@@ -6584,28 +6584,28 @@
         <v>193</v>
       </c>
       <c r="B194" t="str">
-        <v>Jubilant Foodworks Limited</v>
+        <v>Maruti Suzuki India Limited</v>
       </c>
       <c r="C194" t="str">
-        <v>JUBLFOOD</v>
+        <v>MARUTI</v>
       </c>
       <c r="D194" s="1">
-        <v>416.05</v>
+        <v>11251</v>
       </c>
       <c r="E194" s="2">
-        <v>-1.58</v>
+        <v>-0.57</v>
       </c>
       <c r="F194" s="2">
-        <v>-1.58</v>
+        <v>-1.48</v>
       </c>
       <c r="G194" s="2">
-        <v>-8.9</v>
+        <v>-5.98</v>
       </c>
       <c r="H194" s="2">
-        <v>-25.52</v>
+        <v>-32.62</v>
       </c>
       <c r="I194" s="1">
-        <v>1564264</v>
+        <v>746904</v>
       </c>
       <c r="J194" t="str">
         <v/>
@@ -6616,28 +6616,28 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>National Aluminium Company Limited</v>
+        <v>IDFC First Bank Ltd</v>
       </c>
       <c r="C195" t="str">
-        <v>NATIONALUM</v>
+        <v>IDFCFIRSTB</v>
       </c>
       <c r="D195" s="1">
-        <v>310.8</v>
+        <v>78.99</v>
       </c>
       <c r="E195" s="2">
-        <v>-1.61</v>
+        <v>-0.57</v>
       </c>
       <c r="F195" s="2">
-        <v>-1.61</v>
+        <v>-0.67</v>
       </c>
       <c r="G195" s="2">
-        <v>-8.84</v>
+        <v>-3.01</v>
       </c>
       <c r="H195" s="2">
-        <v>-1.11</v>
+        <v>-7.73</v>
       </c>
       <c r="I195" s="1">
-        <v>3501215</v>
+        <v>9496069</v>
       </c>
       <c r="J195" t="str">
         <v/>
@@ -6648,28 +6648,28 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Coal India Limited</v>
+        <v>Eternal Ltd</v>
       </c>
       <c r="C196" t="str">
-        <v>COALINDIA</v>
+        <v>ETERNAL</v>
       </c>
       <c r="D196" s="1">
-        <v>404.8</v>
+        <v>320.45</v>
       </c>
       <c r="E196" s="2">
-        <v>-1.64</v>
+        <v>-0.79</v>
       </c>
       <c r="F196" s="2">
-        <v>-1.64</v>
+        <v>-0.93</v>
       </c>
       <c r="G196" s="2">
-        <v>-4.75</v>
+        <v>0.14</v>
       </c>
       <c r="H196" s="2">
-        <v>1.45</v>
+        <v>15.25</v>
       </c>
       <c r="I196" s="1">
-        <v>10160155</v>
+        <v>18311150</v>
       </c>
       <c r="J196" t="str">
         <v/>
@@ -6680,28 +6680,28 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>Adani Power Limited</v>
+        <v>FSN E-Commerce Ventures Ltd</v>
       </c>
       <c r="C197" t="str">
-        <v>ADANIPOWER</v>
+        <v>NYKAA</v>
       </c>
       <c r="D197" s="1">
-        <v>185.9</v>
+        <v>337.1</v>
       </c>
       <c r="E197" s="2">
-        <v>-1.64</v>
+        <v>-0.85</v>
       </c>
       <c r="F197" s="2">
-        <v>-1.64</v>
+        <v>-1.72</v>
       </c>
       <c r="G197" s="2">
-        <v>-8.87</v>
+        <v>5.34</v>
       </c>
       <c r="H197" s="2">
-        <v>30.01</v>
+        <v>27.14</v>
       </c>
       <c r="I197" s="1">
-        <v>13331869</v>
+        <v>6982487</v>
       </c>
       <c r="J197" t="str">
         <v/>
@@ -6712,28 +6712,28 @@
         <v>197</v>
       </c>
       <c r="B198" t="str">
-        <v>Varun Beverages Limited</v>
+        <v>Kotak Mahindra Bank Limited</v>
       </c>
       <c r="C198" t="str">
-        <v>VBL</v>
+        <v>KOTAKBANK</v>
       </c>
       <c r="D198" s="1">
-        <v>433.3</v>
+        <v>439</v>
       </c>
       <c r="E198" s="2">
-        <v>-1.75</v>
+        <v>-0.99</v>
       </c>
       <c r="F198" s="2">
-        <v>-1.75</v>
+        <v>-0.45</v>
       </c>
       <c r="G198" s="2">
-        <v>0.3</v>
+        <v>5.28</v>
       </c>
       <c r="H198" s="2">
-        <v>-11.54</v>
+        <v>-0.28</v>
       </c>
       <c r="I198" s="1">
-        <v>4053889</v>
+        <v>20411091</v>
       </c>
       <c r="J198" t="str">
         <v/>
@@ -6744,28 +6744,28 @@
         <v>198</v>
       </c>
       <c r="B199" t="str">
-        <v>Swiggy Ltd</v>
+        <v>Tube Investments of India Ltd</v>
       </c>
       <c r="C199" t="str">
-        <v>SWIGGY</v>
+        <v>TIINDIA</v>
       </c>
       <c r="D199" s="1">
-        <v>230</v>
+        <v>2191</v>
       </c>
       <c r="E199" s="2">
-        <v>-1.79</v>
+        <v>-1.04</v>
       </c>
       <c r="F199" s="2">
-        <v>-1.79</v>
+        <v>-0.99</v>
       </c>
       <c r="G199" s="2">
-        <v>-8.04</v>
+        <v>-7.75</v>
       </c>
       <c r="H199" s="2">
-        <v>-40.45</v>
+        <v>-16.19</v>
       </c>
       <c r="I199" s="1">
-        <v>5526494</v>
+        <v>1198053</v>
       </c>
       <c r="J199" t="str">
         <v/>
@@ -6776,28 +6776,28 @@
         <v>199</v>
       </c>
       <c r="B200" t="str">
-        <v>Sagility India Ltd</v>
+        <v>Solar Industries India Limited</v>
       </c>
       <c r="C200" t="str">
-        <v>SAGILITY</v>
+        <v>SOLARINDS</v>
       </c>
       <c r="D200" s="1">
-        <v>43.19</v>
+        <v>20120</v>
       </c>
       <c r="E200" s="2">
-        <v>-1.84</v>
+        <v>-1.05</v>
       </c>
       <c r="F200" s="2">
-        <v>-1.84</v>
+        <v>0.6</v>
       </c>
       <c r="G200" s="2">
-        <v>1.43</v>
+        <v>2.13</v>
       </c>
       <c r="H200" s="2">
-        <v>-16.97</v>
+        <v>64.22</v>
       </c>
       <c r="I200" s="1">
-        <v>5958317</v>
+        <v>94573</v>
       </c>
       <c r="J200" t="str">
         <v/>
@@ -6808,28 +6808,28 @@
         <v>200</v>
       </c>
       <c r="B201" t="str">
-        <v>State Bank Of India Ltd</v>
+        <v>Jsw Energy Limited</v>
       </c>
       <c r="C201" t="str">
-        <v>SBIN</v>
+        <v>JSWENERGY</v>
       </c>
       <c r="D201" s="1">
-        <v>941</v>
+        <v>462.2</v>
       </c>
       <c r="E201" s="2">
-        <v>-1.89</v>
+        <v>-1.1</v>
       </c>
       <c r="F201" s="2">
-        <v>-1.89</v>
+        <v>-0.02</v>
       </c>
       <c r="G201" s="2">
-        <v>-1.93</v>
+        <v>-6.57</v>
       </c>
       <c r="H201" s="2">
-        <v>-4.19</v>
+        <v>-4.2</v>
       </c>
       <c r="I201" s="1">
-        <v>9306202</v>
+        <v>2690015</v>
       </c>
       <c r="J201" t="str">
         <v/>
@@ -6840,28 +6840,28 @@
         <v>201</v>
       </c>
       <c r="B202" t="str">
-        <v>Indian Bank Ltd</v>
+        <v>Hindustan Petroleum Corporation Limited</v>
       </c>
       <c r="C202" t="str">
-        <v>INDIANB</v>
+        <v>HINDPETRO</v>
       </c>
       <c r="D202" s="1">
-        <v>814.1</v>
+        <v>328.4</v>
       </c>
       <c r="E202" s="2">
-        <v>-1.89</v>
+        <v>-1.16</v>
       </c>
       <c r="F202" s="2">
-        <v>-1.89</v>
+        <v>0.74</v>
       </c>
       <c r="G202" s="2">
-        <v>1.02</v>
+        <v>-6.27</v>
       </c>
       <c r="H202" s="2">
-        <v>-2.77</v>
+        <v>-34.2</v>
       </c>
       <c r="I202" s="1">
-        <v>711958</v>
+        <v>4162168</v>
       </c>
       <c r="J202" t="str">
         <v/>
@@ -6872,28 +6872,28 @@
         <v>202</v>
       </c>
       <c r="B203" t="str">
-        <v>Hindustan Unilever Limited</v>
+        <v>Torrent Pharmaceuticals Limited</v>
       </c>
       <c r="C203" t="str">
-        <v>HINDUNILVR</v>
+        <v>TORNTPHARM</v>
       </c>
       <c r="D203" s="1">
-        <v>1820.7</v>
+        <v>4626.4</v>
       </c>
       <c r="E203" s="2">
-        <v>-1.94</v>
+        <v>-1.19</v>
       </c>
       <c r="F203" s="2">
-        <v>-1.94</v>
+        <v>-0.65</v>
       </c>
       <c r="G203" s="2">
-        <v>-3.11</v>
+        <v>-3.62</v>
       </c>
       <c r="H203" s="2">
-        <v>-21.38</v>
+        <v>20.17</v>
       </c>
       <c r="I203" s="1">
-        <v>1479326</v>
+        <v>167791</v>
       </c>
       <c r="J203" t="str">
         <v/>
@@ -6904,28 +6904,28 @@
         <v>203</v>
       </c>
       <c r="B204" t="str">
-        <v>Hindalco Industries Limited</v>
+        <v>Lic Housing Finance Limited</v>
       </c>
       <c r="C204" t="str">
-        <v>HINDALCO</v>
+        <v>LICHSGFIN</v>
       </c>
       <c r="D204" s="1">
-        <v>882.5</v>
+        <v>561</v>
       </c>
       <c r="E204" s="2">
-        <v>-1.98</v>
+        <v>-1.23</v>
       </c>
       <c r="F204" s="2">
-        <v>-1.98</v>
+        <v>1.69</v>
       </c>
       <c r="G204" s="2">
-        <v>-6.3</v>
+        <v>5.81</v>
       </c>
       <c r="H204" s="2">
-        <v>-0.47</v>
+        <v>3.98</v>
       </c>
       <c r="I204" s="1">
-        <v>2605830</v>
+        <v>1816136</v>
       </c>
       <c r="J204" t="str">
         <v/>
@@ -6936,28 +6936,28 @@
         <v>204</v>
       </c>
       <c r="B205" t="str">
-        <v>Max Healthcare Institute Ltd</v>
+        <v>Mankind Pharma Ltd</v>
       </c>
       <c r="C205" t="str">
-        <v>MAXHEALTH</v>
+        <v>MANKIND</v>
       </c>
       <c r="D205" s="1">
-        <v>865.95</v>
+        <v>2369.6</v>
       </c>
       <c r="E205" s="2">
-        <v>-2.02</v>
+        <v>-1.27</v>
       </c>
       <c r="F205" s="2">
-        <v>-2.02</v>
+        <v>0.05</v>
       </c>
       <c r="G205" s="2">
-        <v>-6.87</v>
+        <v>-5.36</v>
       </c>
       <c r="H205" s="2">
-        <v>-17.14</v>
+        <v>7.88</v>
       </c>
       <c r="I205" s="1">
-        <v>2033396</v>
+        <v>319397</v>
       </c>
       <c r="J205" t="str">
         <v/>
@@ -6968,28 +6968,28 @@
         <v>205</v>
       </c>
       <c r="B206" t="str">
-        <v>Nmdc Limited</v>
+        <v>Aurobindo Pharma Limited</v>
       </c>
       <c r="C206" t="str">
-        <v>NMDC</v>
+        <v>AUROPHARMA</v>
       </c>
       <c r="D206" s="1">
-        <v>70.34</v>
+        <v>1685</v>
       </c>
       <c r="E206" s="2">
-        <v>-2.03</v>
+        <v>-1.28</v>
       </c>
       <c r="F206" s="2">
-        <v>-2.03</v>
+        <v>-0.47</v>
       </c>
       <c r="G206" s="2">
-        <v>-8.1</v>
+        <v>0.78</v>
       </c>
       <c r="H206" s="2">
-        <v>-15.43</v>
+        <v>42.43</v>
       </c>
       <c r="I206" s="1">
-        <v>15649136</v>
+        <v>913893</v>
       </c>
       <c r="J206" t="str">
         <v/>
@@ -7000,28 +7000,28 @@
         <v>206</v>
       </c>
       <c r="B207" t="str">
-        <v>Larsen &amp; Toubro Limited</v>
+        <v>Ather Energy Ltd</v>
       </c>
       <c r="C207" t="str">
-        <v>LT</v>
+        <v>ATHERENERG</v>
       </c>
       <c r="D207" s="1">
-        <v>3627.5</v>
+        <v>1490.5</v>
       </c>
       <c r="E207" s="2">
-        <v>-2.05</v>
+        <v>-1.36</v>
       </c>
       <c r="F207" s="2">
-        <v>-2.05</v>
+        <v>3.91</v>
       </c>
       <c r="G207" s="2">
-        <v>-3.52</v>
+        <v>4.6</v>
       </c>
       <c r="H207" s="2">
-        <v>-11.17</v>
+        <v>97.48</v>
       </c>
       <c r="I207" s="1">
-        <v>1177475</v>
+        <v>2200420</v>
       </c>
       <c r="J207" t="str">
         <v/>
@@ -7032,28 +7032,28 @@
         <v>207</v>
       </c>
       <c r="B208" t="str">
-        <v>Vodafone Idea Ltd</v>
+        <v>Polycab India Ltd</v>
       </c>
       <c r="C208" t="str">
-        <v>IDEA</v>
+        <v>POLYCAB</v>
       </c>
       <c r="D208" s="1">
-        <v>12.67</v>
+        <v>8280</v>
       </c>
       <c r="E208" s="2">
-        <v>-2.54</v>
+        <v>-1.49</v>
       </c>
       <c r="F208" s="2">
-        <v>-2.54</v>
+        <v>0.3</v>
       </c>
       <c r="G208" s="2">
-        <v>-2.16</v>
+        <v>3.16</v>
       </c>
       <c r="H208" s="2">
-        <v>17.75</v>
+        <v>8.68</v>
       </c>
       <c r="I208" s="1">
-        <v>327681526</v>
+        <v>796057</v>
       </c>
       <c r="J208" t="str">
         <v/>
@@ -7064,28 +7064,28 @@
         <v>208</v>
       </c>
       <c r="B209" t="str">
-        <v>Colgate Palmolive (india) Limited</v>
+        <v>GE Vernova T&amp;D India Ltd</v>
       </c>
       <c r="C209" t="str">
-        <v>COLPAL</v>
+        <v>GVT&amp;D</v>
       </c>
       <c r="D209" s="1">
-        <v>1767</v>
+        <v>4185</v>
       </c>
       <c r="E209" s="2">
-        <v>-2.79</v>
+        <v>-1.62</v>
       </c>
       <c r="F209" s="2">
-        <v>-2.79</v>
+        <v>-0.22</v>
       </c>
       <c r="G209" s="2">
-        <v>0.21</v>
+        <v>-0.38</v>
       </c>
       <c r="H209" s="2">
-        <v>-14.87</v>
+        <v>33.6</v>
       </c>
       <c r="I209" s="1">
-        <v>769210</v>
+        <v>1083736</v>
       </c>
       <c r="J209" t="str">
         <v/>
@@ -7096,28 +7096,28 @@
         <v>209</v>
       </c>
       <c r="B210" t="str">
-        <v>Tech Mahindra Limited</v>
+        <v>Divi's Laboratories Limited</v>
       </c>
       <c r="C210" t="str">
-        <v>TECHM</v>
+        <v>DIVISLAB</v>
       </c>
       <c r="D210" s="1">
-        <v>1471</v>
+        <v>9272.5</v>
       </c>
       <c r="E210" s="2">
-        <v>-2.85</v>
+        <v>-1.63</v>
       </c>
       <c r="F210" s="2">
-        <v>-2.85</v>
+        <v>-0.72</v>
       </c>
       <c r="G210" s="2">
-        <v>-3.48</v>
+        <v>-0.2</v>
       </c>
       <c r="H210" s="2">
-        <v>-7.54</v>
+        <v>45.05</v>
       </c>
       <c r="I210" s="1">
-        <v>4256937</v>
+        <v>408842</v>
       </c>
       <c r="J210" t="str">
         <v/>
@@ -7128,28 +7128,28 @@
         <v>210</v>
       </c>
       <c r="B211" t="str">
-        <v>GMR Airports Ltd</v>
+        <v>CG Power and Industrial Solutions Ltd</v>
       </c>
       <c r="C211" t="str">
-        <v>GMRAIRPORT</v>
+        <v>CGPOWER</v>
       </c>
       <c r="D211" s="1">
-        <v>89.5</v>
+        <v>853.2</v>
       </c>
       <c r="E211" s="2">
-        <v>-3.04</v>
+        <v>-1.65</v>
       </c>
       <c r="F211" s="2">
-        <v>-3.04</v>
+        <v>-0.27</v>
       </c>
       <c r="G211" s="2">
-        <v>-5.94</v>
+        <v>-0.12</v>
       </c>
       <c r="H211" s="2">
-        <v>-14.25</v>
+        <v>31.69</v>
       </c>
       <c r="I211" s="1">
-        <v>17800127</v>
+        <v>2434801</v>
       </c>
       <c r="J211" t="str">
         <v/>
@@ -7160,28 +7160,28 @@
         <v>211</v>
       </c>
       <c r="B212" t="str">
-        <v>Itc Limited</v>
+        <v>Multi Commodity Exchange Of India Limited</v>
       </c>
       <c r="C212" t="str">
-        <v>ITC</v>
+        <v>MCX</v>
       </c>
       <c r="D212" s="1">
-        <v>257.9</v>
+        <v>3304.9</v>
       </c>
       <c r="E212" s="2">
-        <v>-3.05</v>
+        <v>-2.51</v>
       </c>
       <c r="F212" s="2">
-        <v>-3.05</v>
+        <v>-0.4</v>
       </c>
       <c r="G212" s="2">
-        <v>-1.85</v>
+        <v>0.14</v>
       </c>
       <c r="H212" s="2">
-        <v>-36.01</v>
+        <v>48.39</v>
       </c>
       <c r="I212" s="1">
-        <v>14895734</v>
+        <v>1633229</v>
       </c>
       <c r="J212" t="str">
         <v/>
@@ -7192,28 +7192,28 @@
         <v>212</v>
       </c>
       <c r="B213" t="str">
-        <v>Apollo Hospitals Enterprise Limited</v>
+        <v>Vedanta Limited</v>
       </c>
       <c r="C213" t="str">
-        <v>APOLLOHOSP</v>
+        <v>VEDL</v>
       </c>
       <c r="D213" s="1">
-        <v>7775</v>
+        <v>256.25</v>
       </c>
       <c r="E213" s="2">
-        <v>-3.15</v>
+        <v>-3.27</v>
       </c>
       <c r="F213" s="2">
-        <v>-3.15</v>
+        <v>-2.94</v>
       </c>
       <c r="G213" s="2">
-        <v>-4.78</v>
+        <v>-1.06</v>
       </c>
       <c r="H213" s="2">
-        <v>10.4</v>
+        <v>17.19</v>
       </c>
       <c r="I213" s="1">
-        <v>990813</v>
+        <v>18993398</v>
       </c>
       <c r="J213" t="str">
         <v/>
@@ -7224,28 +7224,28 @@
         <v>213</v>
       </c>
       <c r="B214" t="str">
-        <v>Dabur India Limited</v>
+        <v>Hitachi Energy India Ltd</v>
       </c>
       <c r="C214" t="str">
-        <v>DABUR</v>
+        <v>POWERINDIA</v>
       </c>
       <c r="D214" s="1">
-        <v>374.4</v>
+        <v>30250</v>
       </c>
       <c r="E214" s="2">
-        <v>-3.18</v>
+        <v>-3.32</v>
       </c>
       <c r="F214" s="2">
-        <v>-3.18</v>
+        <v>-1.16</v>
       </c>
       <c r="G214" s="2">
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="H214" s="2">
-        <v>-25.66</v>
+        <v>65.21</v>
       </c>
       <c r="I214" s="1">
-        <v>1816189</v>
+        <v>197670</v>
       </c>
       <c r="J214" t="str">
         <v/>
@@ -7256,28 +7256,28 @@
         <v>214</v>
       </c>
       <c r="B215" t="str">
-        <v>Fortis Healthcare Limited</v>
+        <v>Icici Prudential Life Insurance Company Limited</v>
       </c>
       <c r="C215" t="str">
-        <v>FORTIS</v>
+        <v>ICICIPRULI</v>
       </c>
       <c r="D215" s="1">
-        <v>757.25</v>
+        <v>447.45</v>
       </c>
       <c r="E215" s="2">
-        <v>-3.69</v>
+        <v>-3.44</v>
       </c>
       <c r="F215" s="2">
-        <v>-3.69</v>
+        <v>-2.84</v>
       </c>
       <c r="G215" s="2">
-        <v>-1.66</v>
+        <v>0.82</v>
       </c>
       <c r="H215" s="2">
-        <v>-14.34</v>
+        <v>-33.04</v>
       </c>
       <c r="I215" s="1">
-        <v>998167</v>
+        <v>3061445</v>
       </c>
       <c r="J215" t="str">
         <v/>
@@ -7288,28 +7288,28 @@
         <v>215</v>
       </c>
       <c r="B216" t="str">
-        <v>Avenue Supermarts Ltd</v>
+        <v>Rbl Bank Limited</v>
       </c>
       <c r="C216" t="str">
-        <v>DMART</v>
+        <v>RBLBANK</v>
       </c>
       <c r="D216" s="1">
-        <v>3364.9</v>
+        <v>388.3</v>
       </c>
       <c r="E216" s="2">
-        <v>-4.32</v>
+        <v>-7.04</v>
       </c>
       <c r="F216" s="2">
-        <v>-4.32</v>
+        <v>-7.11</v>
       </c>
       <c r="G216" s="2">
-        <v>-11.48</v>
+        <v>-3.73</v>
       </c>
       <c r="H216" s="2">
-        <v>-11.03</v>
+        <v>22.96</v>
       </c>
       <c r="I216" s="1">
-        <v>3131384</v>
+        <v>39152113</v>
       </c>
       <c r="J216" t="str">
         <v/>
